--- a/spreadsheets/2026 Fin Inst Database.xlsx
+++ b/spreadsheets/2026 Fin Inst Database.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micha\git-crypto\spreadsheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micha\git-projects\trading\spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B03F8B23-5F1B-49CE-9306-1D5CDE236B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F64171-18C8-4B5B-80CD-D8ACAFBFB4F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="22425" windowHeight="12825" tabRatio="763" activeTab="3" xr2:uid="{80E421DC-2A5F-48BD-91BD-DB367A6ED94D}"/>
+    <workbookView xWindow="375" yWindow="2070" windowWidth="28290" windowHeight="12210" tabRatio="763" firstSheet="3" activeTab="3" xr2:uid="{80E421DC-2A5F-48BD-91BD-DB367A6ED94D}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="31" r:id="rId1"/>
@@ -2523,6 +2523,138 @@
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -3354,138 +3486,6 @@
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3615,34 +3615,34 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D0B1F78D-D1AA-4EF3-9596-7A27A355C060}" name="static_data_table" displayName="static_data_table" ref="A1:O121" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63" headerRowCellStyle="Comma" dataCellStyle="Comma">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D0B1F78D-D1AA-4EF3-9596-7A27A355C060}" name="static_data_table" displayName="static_data_table" ref="A1:O121" totalsRowShown="0" headerRowDxfId="71" dataDxfId="70" headerRowCellStyle="Comma" dataCellStyle="Comma">
   <autoFilter ref="A1:O121" xr:uid="{D0B1F78D-D1AA-4EF3-9596-7A27A355C060}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R42">
     <sortCondition ref="F1:F73"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="19" xr3:uid="{1221CC04-A25D-42E0-9BD3-B46333797DBE}" name="vpn" dataDxfId="62" dataCellStyle="Comma"/>
-    <tableColumn id="10" xr3:uid="{BED55A9A-3E28-4A17-AA02-2381DB89A658}" name="family" dataDxfId="61" dataCellStyle="Comma"/>
-    <tableColumn id="12" xr3:uid="{F9B08B7F-16AE-460B-BDFB-B2726D177E92}" name="sub_family" dataDxfId="60" dataCellStyle="Comma"/>
-    <tableColumn id="1" xr3:uid="{8C59AB6B-6EBF-48B8-9D8A-4E9EFB96C425}" name="my_prod_type" dataDxfId="59"/>
-    <tableColumn id="18" xr3:uid="{D3CEE51C-FF16-474C-AC93-30CEB3E7D375}" name="my_fi_name" dataDxfId="58" dataCellStyle="Comma"/>
-    <tableColumn id="22" xr3:uid="{51F924B8-25BB-4080-AD58-7509A60E27B0}" name="my_pf_name" dataDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{A13A7736-F17C-4146-B643-6EF65FC4B25C}" name="pf_locator" dataDxfId="56"/>
-    <tableColumn id="4" xr3:uid="{211C7B2F-2849-4B0F-B281-BF0424C5B57F}" name="top_currency" dataDxfId="55" dataCellStyle="Comma"/>
-    <tableColumn id="3" xr3:uid="{46C5F41D-D64D-4F76-9E5D-390D6FE03BE6}" name="base_currency" dataDxfId="54" dataCellStyle="Comma"/>
-    <tableColumn id="9" xr3:uid="{E2441BE5-ABB7-40CB-848F-02508F05A37C}" name="comm_type" dataDxfId="53" dataCellStyle="Comma"/>
-    <tableColumn id="5" xr3:uid="{16FCE019-989B-4467-A8B9-96A8E58B2A2A}" name="comm_maker" dataDxfId="52" dataCellStyle="Currency"/>
-    <tableColumn id="6" xr3:uid="{0E805949-D535-4626-85EB-FA3727E7DAF4}" name="comm_taker" dataDxfId="51" dataCellStyle="Currency"/>
-    <tableColumn id="7" xr3:uid="{5709324A-7C63-43F4-AF59-F119177A7972}" name="comm_misc" dataDxfId="50" dataCellStyle="Comma"/>
-    <tableColumn id="8" xr3:uid="{32E47B88-05FD-48EE-97A0-59BC78476043}" name="comm_update" dataDxfId="49" dataCellStyle="Comma"/>
-    <tableColumn id="11" xr3:uid="{B6578BCD-793E-47C9-99CF-D01D02E8D922}" name="mkt_data_stream" dataDxfId="48" dataCellStyle="Comma"/>
+    <tableColumn id="19" xr3:uid="{1221CC04-A25D-42E0-9BD3-B46333797DBE}" name="vpn" dataDxfId="69" dataCellStyle="Comma"/>
+    <tableColumn id="10" xr3:uid="{BED55A9A-3E28-4A17-AA02-2381DB89A658}" name="family" dataDxfId="68" dataCellStyle="Comma"/>
+    <tableColumn id="12" xr3:uid="{F9B08B7F-16AE-460B-BDFB-B2726D177E92}" name="sub_family" dataDxfId="67" dataCellStyle="Comma"/>
+    <tableColumn id="1" xr3:uid="{8C59AB6B-6EBF-48B8-9D8A-4E9EFB96C425}" name="my_prod_type" dataDxfId="66"/>
+    <tableColumn id="18" xr3:uid="{D3CEE51C-FF16-474C-AC93-30CEB3E7D375}" name="my_fi_name" dataDxfId="65" dataCellStyle="Comma"/>
+    <tableColumn id="22" xr3:uid="{51F924B8-25BB-4080-AD58-7509A60E27B0}" name="my_pf_name" dataDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{A13A7736-F17C-4146-B643-6EF65FC4B25C}" name="pf_locator" dataDxfId="63"/>
+    <tableColumn id="4" xr3:uid="{211C7B2F-2849-4B0F-B281-BF0424C5B57F}" name="top_currency" dataDxfId="62" dataCellStyle="Comma"/>
+    <tableColumn id="3" xr3:uid="{46C5F41D-D64D-4F76-9E5D-390D6FE03BE6}" name="base_currency" dataDxfId="61" dataCellStyle="Comma"/>
+    <tableColumn id="9" xr3:uid="{E2441BE5-ABB7-40CB-848F-02508F05A37C}" name="comm_type" dataDxfId="60" dataCellStyle="Comma"/>
+    <tableColumn id="5" xr3:uid="{16FCE019-989B-4467-A8B9-96A8E58B2A2A}" name="comm_maker" dataDxfId="59" dataCellStyle="Currency"/>
+    <tableColumn id="6" xr3:uid="{0E805949-D535-4626-85EB-FA3727E7DAF4}" name="comm_taker" dataDxfId="58" dataCellStyle="Currency"/>
+    <tableColumn id="7" xr3:uid="{5709324A-7C63-43F4-AF59-F119177A7972}" name="comm_misc" dataDxfId="57" dataCellStyle="Comma"/>
+    <tableColumn id="8" xr3:uid="{32E47B88-05FD-48EE-97A0-59BC78476043}" name="comm_update" dataDxfId="56" dataCellStyle="Comma"/>
+    <tableColumn id="11" xr3:uid="{B6578BCD-793E-47C9-99CF-D01D02E8D922}" name="mkt_data_stream" dataDxfId="55" dataCellStyle="Comma"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{8AFBE59F-E145-48B4-A9F0-75F818F296F4}" name="btc_to_do" displayName="btc_to_do" ref="A126:AA179" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{8AFBE59F-E145-48B4-A9F0-75F818F296F4}" name="btc_to_do" displayName="btc_to_do" ref="A126:AA179" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53">
   <autoFilter ref="A126:AA179" xr:uid="{8AFBE59F-E145-48B4-A9F0-75F818F296F4}">
     <filterColumn colId="1">
       <filters>
@@ -3651,47 +3651,47 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{73FD62E2-E8FE-4C00-9C3C-F3122EB55D0D}" name="Column1" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{F8F856BF-80BD-4398-8276-448953D1A283}" name="Column2" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{859FF76C-0D7F-496C-B885-2DE680F3F916}" name="Column7" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{EFE5B159-5688-4C13-A02D-A6C704275E2E}" name="Column4" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{69D00D15-DF82-46C9-9945-107A85371A6F}" name="Column5" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{F10DE59E-3B92-4DD0-8A04-FAE76E9F8BB9}" name="Column6" dataDxfId="40"/>
-    <tableColumn id="8" xr3:uid="{2D949549-0F5C-4A89-B8F7-72304B9A24F1}" name="Column8" dataDxfId="39"/>
-    <tableColumn id="9" xr3:uid="{C42826CE-029E-4945-8434-CBC9F4DAA57F}" name="Column9" dataDxfId="38" dataCellStyle="Comma"/>
-    <tableColumn id="7" xr3:uid="{F0789B57-A27F-47CD-94AE-4F6B71344DB9}" name="Column92" dataDxfId="37" dataCellStyle="Currency"/>
-    <tableColumn id="13" xr3:uid="{84F8B5AD-93FB-4C3E-8E09-FB358E10FC62}" name="Column93" dataDxfId="36" dataCellStyle="Currency"/>
-    <tableColumn id="14" xr3:uid="{DA8CB162-5C11-45A4-93E0-E0C45C3ED3D0}" name="Column94" dataDxfId="35" dataCellStyle="Comma"/>
-    <tableColumn id="27" xr3:uid="{100A9F62-6915-49BB-B014-4D0BC03BB553}" name="Column95" dataDxfId="34" dataCellStyle="Comma"/>
-    <tableColumn id="10" xr3:uid="{5B60D48A-2B91-4E81-AD9D-2709C1335F32}" name="Column10" dataDxfId="33" dataCellStyle="Comma"/>
-    <tableColumn id="11" xr3:uid="{E1B16D3B-DEA4-44A7-8DE4-CA3F41D77B2B}" name="Column11" dataDxfId="32" dataCellStyle="Comma"/>
-    <tableColumn id="12" xr3:uid="{793817C6-38BE-49BA-A9A6-4F96D87310D9}" name="Column12" dataDxfId="31" dataCellStyle="Comma"/>
-    <tableColumn id="15" xr3:uid="{2AFA675A-D2B0-476D-A865-BB72634DC6DA}" name="Column15" dataDxfId="30"/>
-    <tableColumn id="16" xr3:uid="{B5249436-7148-4EBF-B8E6-5226AA101320}" name="Column16" dataDxfId="29" dataCellStyle="Currency"/>
-    <tableColumn id="17" xr3:uid="{22140E2C-B2EC-4771-8D39-0E8FE9F80B88}" name="Column17" dataDxfId="28"/>
-    <tableColumn id="18" xr3:uid="{AC423A03-E794-4524-9C7D-D02B01892118}" name="Column18" dataDxfId="27" dataCellStyle="Comma"/>
-    <tableColumn id="19" xr3:uid="{F73A917A-F13B-4BB9-8524-E34E6050878C}" name="Column19" dataDxfId="26" dataCellStyle="Comma"/>
-    <tableColumn id="20" xr3:uid="{4A9B484B-EBD7-41D1-8470-161DB87D7FB2}" name="Column20" dataDxfId="25" dataCellStyle="Comma"/>
-    <tableColumn id="21" xr3:uid="{D03D1805-69BB-4D67-B61E-961F2E625E81}" name="Column21" dataDxfId="24"/>
-    <tableColumn id="22" xr3:uid="{66E8E4D1-FF14-404F-8354-025C93AED5CB}" name="Column22" dataDxfId="23"/>
-    <tableColumn id="23" xr3:uid="{9540F131-1C8F-4F4F-8796-92F1AFD57E03}" name="Column23" dataDxfId="22"/>
-    <tableColumn id="24" xr3:uid="{B7156378-CEA1-4808-9801-4E93C755FE92}" name="Column24" dataDxfId="21"/>
-    <tableColumn id="25" xr3:uid="{6908C233-AA1B-4818-BF8F-36FC13C53D09}" name="Column25" dataDxfId="20"/>
-    <tableColumn id="26" xr3:uid="{104781D6-1EEE-4947-A424-3CE3DCADF4CF}" name="Column26" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{73FD62E2-E8FE-4C00-9C3C-F3122EB55D0D}" name="Column1" dataDxfId="52"/>
+    <tableColumn id="2" xr3:uid="{F8F856BF-80BD-4398-8276-448953D1A283}" name="Column2" dataDxfId="51"/>
+    <tableColumn id="3" xr3:uid="{859FF76C-0D7F-496C-B885-2DE680F3F916}" name="Column7" dataDxfId="50"/>
+    <tableColumn id="4" xr3:uid="{EFE5B159-5688-4C13-A02D-A6C704275E2E}" name="Column4" dataDxfId="49"/>
+    <tableColumn id="5" xr3:uid="{69D00D15-DF82-46C9-9945-107A85371A6F}" name="Column5" dataDxfId="48"/>
+    <tableColumn id="6" xr3:uid="{F10DE59E-3B92-4DD0-8A04-FAE76E9F8BB9}" name="Column6" dataDxfId="47"/>
+    <tableColumn id="8" xr3:uid="{2D949549-0F5C-4A89-B8F7-72304B9A24F1}" name="Column8" dataDxfId="46"/>
+    <tableColumn id="9" xr3:uid="{C42826CE-029E-4945-8434-CBC9F4DAA57F}" name="Column9" dataDxfId="45" dataCellStyle="Comma"/>
+    <tableColumn id="7" xr3:uid="{F0789B57-A27F-47CD-94AE-4F6B71344DB9}" name="Column92" dataDxfId="44" dataCellStyle="Currency"/>
+    <tableColumn id="13" xr3:uid="{84F8B5AD-93FB-4C3E-8E09-FB358E10FC62}" name="Column93" dataDxfId="43" dataCellStyle="Currency"/>
+    <tableColumn id="14" xr3:uid="{DA8CB162-5C11-45A4-93E0-E0C45C3ED3D0}" name="Column94" dataDxfId="42" dataCellStyle="Comma"/>
+    <tableColumn id="27" xr3:uid="{100A9F62-6915-49BB-B014-4D0BC03BB553}" name="Column95" dataDxfId="41" dataCellStyle="Comma"/>
+    <tableColumn id="10" xr3:uid="{5B60D48A-2B91-4E81-AD9D-2709C1335F32}" name="Column10" dataDxfId="40" dataCellStyle="Comma"/>
+    <tableColumn id="11" xr3:uid="{E1B16D3B-DEA4-44A7-8DE4-CA3F41D77B2B}" name="Column11" dataDxfId="39" dataCellStyle="Comma"/>
+    <tableColumn id="12" xr3:uid="{793817C6-38BE-49BA-A9A6-4F96D87310D9}" name="Column12" dataDxfId="38" dataCellStyle="Comma"/>
+    <tableColumn id="15" xr3:uid="{2AFA675A-D2B0-476D-A865-BB72634DC6DA}" name="Column15" dataDxfId="37"/>
+    <tableColumn id="16" xr3:uid="{B5249436-7148-4EBF-B8E6-5226AA101320}" name="Column16" dataDxfId="36" dataCellStyle="Currency"/>
+    <tableColumn id="17" xr3:uid="{22140E2C-B2EC-4771-8D39-0E8FE9F80B88}" name="Column17" dataDxfId="35"/>
+    <tableColumn id="18" xr3:uid="{AC423A03-E794-4524-9C7D-D02B01892118}" name="Column18" dataDxfId="34" dataCellStyle="Comma"/>
+    <tableColumn id="19" xr3:uid="{F73A917A-F13B-4BB9-8524-E34E6050878C}" name="Column19" dataDxfId="33" dataCellStyle="Comma"/>
+    <tableColumn id="20" xr3:uid="{4A9B484B-EBD7-41D1-8470-161DB87D7FB2}" name="Column20" dataDxfId="32" dataCellStyle="Comma"/>
+    <tableColumn id="21" xr3:uid="{D03D1805-69BB-4D67-B61E-961F2E625E81}" name="Column21" dataDxfId="31"/>
+    <tableColumn id="22" xr3:uid="{66E8E4D1-FF14-404F-8354-025C93AED5CB}" name="Column22" dataDxfId="30"/>
+    <tableColumn id="23" xr3:uid="{9540F131-1C8F-4F4F-8796-92F1AFD57E03}" name="Column23" dataDxfId="29"/>
+    <tableColumn id="24" xr3:uid="{B7156378-CEA1-4808-9801-4E93C755FE92}" name="Column24" dataDxfId="28"/>
+    <tableColumn id="25" xr3:uid="{6908C233-AA1B-4818-BF8F-36FC13C53D09}" name="Column25" dataDxfId="27"/>
+    <tableColumn id="26" xr3:uid="{104781D6-1EEE-4947-A424-3CE3DCADF4CF}" name="Column26" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D7EA60E1-CEC4-43C9-8716-3B5D84C5EEA2}" name="mkt_data_streaming_inputs" displayName="mkt_data_streaming_inputs" ref="A1:E13" totalsRowShown="0" headerRowDxfId="71" dataDxfId="70">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D7EA60E1-CEC4-43C9-8716-3B5D84C5EEA2}" name="mkt_data_streaming_inputs" displayName="mkt_data_streaming_inputs" ref="A1:E13" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
   <autoFilter ref="A1:E13" xr:uid="{D7EA60E1-CEC4-43C9-8716-3B5D84C5EEA2}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{1B4EEA70-C71C-4CEF-9887-9E40B33F8AAC}" name="Keys" dataDxfId="69"/>
-    <tableColumn id="2" xr3:uid="{5215E933-000B-4891-AE18-89796F5A216B}" name="Crypto" dataDxfId="68"/>
-    <tableColumn id="3" xr3:uid="{6EAA8208-3724-49EE-BF7B-16658A7D02A7}" name="Stat_Arb_Pairs" dataDxfId="67"/>
-    <tableColumn id="4" xr3:uid="{A4E0A8E0-4334-4FB9-95BD-3E9FE4AB471E}" name="Stat_Arb_Group" dataDxfId="66"/>
-    <tableColumn id="5" xr3:uid="{16DC4587-9A67-4643-BE5B-698CEC2360C4}" name="BTC_ETF" dataDxfId="65"/>
+    <tableColumn id="1" xr3:uid="{1B4EEA70-C71C-4CEF-9887-9E40B33F8AAC}" name="Keys" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{5215E933-000B-4891-AE18-89796F5A216B}" name="Crypto" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{6EAA8208-3724-49EE-BF7B-16658A7D02A7}" name="Stat_Arb_Pairs" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{A4E0A8E0-4334-4FB9-95BD-3E9FE4AB471E}" name="Stat_Arb_Group" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{16DC4587-9A67-4643-BE5B-698CEC2360C4}" name="BTC_ETF" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14442,7 +14442,7 @@
       </c>
       <c r="E5" s="193" t="str">
         <f ca="1">_xlfn.CONCAT("ETF_",E15,".csv")</f>
-        <v>ETF_2026-08-20.csv</v>
+        <v>ETF_2026-08-21.csv</v>
       </c>
       <c r="F5" s="171"/>
     </row>
@@ -14595,7 +14595,7 @@
     <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E15" s="197" t="str">
         <f t="shared" ref="E15" ca="1" si="0">TEXT(TODAY(),"yyyy-mm-dd")</f>
-        <v>2026-08-20</v>
+        <v>2026-08-21</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.2">

--- a/spreadsheets/2026 Fin Inst Database.xlsx
+++ b/spreadsheets/2026 Fin Inst Database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micha\git-projects\trading\spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F64171-18C8-4B5B-80CD-D8ACAFBFB4F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0032E19-EFD5-4E3B-8365-CA3464C57F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="375" yWindow="2070" windowWidth="28290" windowHeight="12210" tabRatio="763" firstSheet="3" activeTab="3" xr2:uid="{80E421DC-2A5F-48BD-91BD-DB367A6ED94D}"/>
+    <workbookView xWindow="2940" yWindow="1665" windowWidth="28290" windowHeight="12210" tabRatio="763" firstSheet="3" activeTab="5" xr2:uid="{80E421DC-2A5F-48BD-91BD-DB367A6ED94D}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="31" r:id="rId1"/>
@@ -1123,9 +1123,6 @@
     <t>active</t>
   </si>
   <si>
-    <t>cd git-crypto\crypto-project\apps</t>
-  </si>
-  <si>
     <t>python App_Stream_MktData.py</t>
   </si>
   <si>
@@ -1283,6 +1280,9 @@
   </si>
   <si>
     <t>2026 Group Trading Inputs.xlsm</t>
+  </si>
+  <si>
+    <t>cd git-project\trading\apps</t>
   </si>
 </sst>
 </file>
@@ -5625,7 +5625,7 @@
         <v>10</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P1" s="6"/>
       <c r="Q1" s="6"/>
@@ -8375,7 +8375,7 @@
         <v>3</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>5</v>
@@ -8682,7 +8682,7 @@
         <v>3</v>
       </c>
       <c r="E63" s="153" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F63" s="153" t="s">
         <v>5</v>
@@ -9243,7 +9243,7 @@
         <v>41</v>
       </c>
       <c r="E74" s="162" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F74" s="161" t="s">
         <v>5</v>
@@ -9344,7 +9344,7 @@
         <v>41</v>
       </c>
       <c r="E76" s="162" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F76" s="161" t="s">
         <v>5</v>
@@ -9394,7 +9394,7 @@
         <v>41</v>
       </c>
       <c r="E77" s="162" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F77" s="161" t="s">
         <v>5</v>
@@ -9441,7 +9441,7 @@
         <v>41</v>
       </c>
       <c r="E78" s="162" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F78" s="161" t="s">
         <v>5</v>
@@ -9491,7 +9491,7 @@
         <v>41</v>
       </c>
       <c r="E79" s="162" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F79" s="161" t="s">
         <v>5</v>
@@ -9541,7 +9541,7 @@
         <v>41</v>
       </c>
       <c r="E80" s="162" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F80" s="161" t="s">
         <v>5</v>
@@ -9641,7 +9641,7 @@
         <v>41</v>
       </c>
       <c r="E82" s="162" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F82" s="161" t="s">
         <v>5</v>
@@ -9691,7 +9691,7 @@
         <v>41</v>
       </c>
       <c r="E83" s="162" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F83" s="161" t="s">
         <v>5</v>
@@ -9791,7 +9791,7 @@
         <v>41</v>
       </c>
       <c r="E85" s="162" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F85" s="161" t="s">
         <v>5</v>
@@ -9841,7 +9841,7 @@
         <v>41</v>
       </c>
       <c r="E86" s="162" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F86" s="161" t="s">
         <v>5</v>
@@ -9891,7 +9891,7 @@
         <v>41</v>
       </c>
       <c r="E87" s="162" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F87" s="161" t="s">
         <v>5</v>
@@ -10041,7 +10041,7 @@
         <v>41</v>
       </c>
       <c r="E90" s="162" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F90" s="161" t="s">
         <v>5</v>
@@ -10091,7 +10091,7 @@
         <v>41</v>
       </c>
       <c r="E91" s="162" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F91" s="161" t="s">
         <v>5</v>
@@ -10141,7 +10141,7 @@
         <v>41</v>
       </c>
       <c r="E92" s="162" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F92" s="161" t="s">
         <v>5</v>
@@ -10191,7 +10191,7 @@
         <v>41</v>
       </c>
       <c r="E93" s="162" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F93" s="161" t="s">
         <v>5</v>
@@ -10341,7 +10341,7 @@
         <v>41</v>
       </c>
       <c r="E96" s="162" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F96" s="161" t="s">
         <v>5</v>
@@ -10391,7 +10391,7 @@
         <v>41</v>
       </c>
       <c r="E97" s="162" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F97" s="161" t="s">
         <v>5</v>
@@ -10441,7 +10441,7 @@
         <v>41</v>
       </c>
       <c r="E98" s="162" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F98" s="161" t="s">
         <v>5</v>
@@ -10491,7 +10491,7 @@
         <v>41</v>
       </c>
       <c r="E99" s="162" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F99" s="161" t="s">
         <v>5</v>
@@ -10591,7 +10591,7 @@
         <v>41</v>
       </c>
       <c r="E101" s="162" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F101" s="161" t="s">
         <v>5</v>
@@ -10641,7 +10641,7 @@
         <v>41</v>
       </c>
       <c r="E102" s="162" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F102" s="161" t="s">
         <v>5</v>
@@ -10691,7 +10691,7 @@
         <v>41</v>
       </c>
       <c r="E103" s="162" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F103" s="161" t="s">
         <v>5</v>
@@ -10741,7 +10741,7 @@
         <v>41</v>
       </c>
       <c r="E104" s="162" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F104" s="161" t="s">
         <v>5</v>
@@ -10791,7 +10791,7 @@
         <v>41</v>
       </c>
       <c r="E105" s="162" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F105" s="161" t="s">
         <v>5</v>
@@ -11091,7 +11091,7 @@
         <v>41</v>
       </c>
       <c r="E111" s="162" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F111" s="161" t="s">
         <v>5</v>
@@ -11141,7 +11141,7 @@
         <v>41</v>
       </c>
       <c r="E112" s="162" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F112" s="161" t="s">
         <v>5</v>
@@ -11191,7 +11191,7 @@
         <v>41</v>
       </c>
       <c r="E113" s="162" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F113" s="161" t="s">
         <v>5</v>
@@ -11391,7 +11391,7 @@
         <v>41</v>
       </c>
       <c r="E117" s="162" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F117" s="161" t="s">
         <v>5</v>
@@ -11491,7 +11491,7 @@
         <v>41</v>
       </c>
       <c r="E119" s="162" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F119" s="161" t="s">
         <v>5</v>
@@ -11541,7 +11541,7 @@
         <v>41</v>
       </c>
       <c r="E120" s="162" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F120" s="161" t="s">
         <v>5</v>
@@ -14364,13 +14364,13 @@
         <v>339</v>
       </c>
       <c r="C1" s="172" t="s">
+        <v>408</v>
+      </c>
+      <c r="D1" s="172" t="s">
+        <v>410</v>
+      </c>
+      <c r="E1" s="172" t="s">
         <v>409</v>
-      </c>
-      <c r="D1" s="172" t="s">
-        <v>411</v>
-      </c>
-      <c r="E1" s="172" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.25">
@@ -14381,7 +14381,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="173" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="173" t="b">
         <v>1</v>
@@ -14435,14 +14435,14 @@
         <v>353</v>
       </c>
       <c r="C5" s="193" t="s">
+        <v>411</v>
+      </c>
+      <c r="D5" s="193" t="s">
         <v>412</v>
-      </c>
-      <c r="D5" s="193" t="s">
-        <v>413</v>
       </c>
       <c r="E5" s="193" t="str">
         <f ca="1">_xlfn.CONCAT("ETF_",E15,".csv")</f>
-        <v>ETF_2026-08-21.csv</v>
+        <v>ETF_2026-08-24.csv</v>
       </c>
       <c r="F5" s="171"/>
     </row>
@@ -14595,17 +14595,17 @@
     <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E15" s="197" t="str">
         <f t="shared" ref="E15" ca="1" si="0">TEXT(TODAY(),"yyyy-mm-dd")</f>
-        <v>2026-08-21</v>
+        <v>2026-08-24</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="195" t="s">
-        <v>360</v>
+        <v>413</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="196" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="25" spans="1:1" s="175" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -14646,24 +14646,24 @@
         <v>184</v>
       </c>
       <c r="B1" s="176" t="s">
+        <v>394</v>
+      </c>
+      <c r="C1" s="176" t="s">
         <v>395</v>
       </c>
-      <c r="C1" s="176" t="s">
+      <c r="D1" s="177" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="177" t="s">
+      <c r="E1" s="178" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="178" t="s">
+      <c r="F1" s="179" t="s">
         <v>398</v>
-      </c>
-      <c r="F1" s="179" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B2" s="180">
         <v>1</v>
@@ -14678,7 +14678,7 @@
         <v>0.33401199999999998</v>
       </c>
       <c r="F2" s="179" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -14698,12 +14698,12 @@
         <v>0.15989999999999999</v>
       </c>
       <c r="F3" s="179" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B4" s="180">
         <v>0.16500000000000001</v>
@@ -14718,12 +14718,12 @@
         <v>0.246638</v>
       </c>
       <c r="F4" s="179" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B5" s="180">
         <v>0.27500000000000002</v>
@@ -14738,12 +14738,12 @@
         <v>0.96860000000000002</v>
       </c>
       <c r="F5" s="179" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B6" s="180">
         <v>1</v>
@@ -14758,12 +14758,12 @@
         <v>0</v>
       </c>
       <c r="F6" s="179" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B7" s="180">
         <v>0.1002</v>
@@ -14778,12 +14778,12 @@
         <v>0.139651</v>
       </c>
       <c r="F7" s="179" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B8" s="180">
         <v>0.16500000000000001</v>
@@ -14798,7 +14798,7 @@
         <v>0.42</v>
       </c>
       <c r="F8" s="179" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -14818,12 +14818,12 @@
         <v>0.16361100000000001</v>
       </c>
       <c r="F9" s="179" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B10" s="180">
         <v>0.16500000000000001</v>
@@ -14838,12 +14838,12 @@
         <v>0.38289299999999998</v>
       </c>
       <c r="F10" s="179" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B11" s="180">
         <v>0.16500000000000001</v>
@@ -14858,7 +14858,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="F11" s="179" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -14878,12 +14878,12 @@
         <v>0.14660500000000001</v>
       </c>
       <c r="F12" s="179" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B13" s="180">
         <v>0.27500000000000002</v>
@@ -14892,12 +14892,12 @@
         <v>4.8999999999999998E-3</v>
       </c>
       <c r="F13" s="179" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B14" s="180">
         <v>1</v>
@@ -14906,12 +14906,12 @@
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="F14" s="179" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B15" s="180">
         <v>1</v>
@@ -14926,7 +14926,7 @@
         <v>1.5387740000000001</v>
       </c>
       <c r="F15" s="179" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -14946,7 +14946,7 @@
         <v>0.21784200000000001</v>
       </c>
       <c r="F16" s="179" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -14966,12 +14966,12 @@
         <v>0.21740999999999999</v>
       </c>
       <c r="F17" s="179" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B18" s="180">
         <v>0.16500000000000001</v>
@@ -14986,12 +14986,12 @@
         <v>0.58702200000000004</v>
       </c>
       <c r="F18" s="179" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B19" s="180">
         <v>0.16500000000000001</v>
@@ -15006,12 +15006,12 @@
         <v>0.164775</v>
       </c>
       <c r="F19" s="179" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B20" s="180">
         <v>0.27500000000000002</v>
@@ -15020,12 +15020,12 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="F20" s="179" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="118" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B21" s="185">
         <v>0.16500000000000001</v>
@@ -15036,7 +15036,7 @@
       <c r="D21" s="187"/>
       <c r="E21" s="188"/>
       <c r="F21" s="189" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G21" s="118"/>
     </row>
@@ -15057,7 +15057,7 @@
         <v>0.33404800000000001</v>
       </c>
       <c r="F22" s="179" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -15077,12 +15077,12 @@
         <v>0.285497</v>
       </c>
       <c r="F23" s="179" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="118" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B24" s="185">
         <v>0.16500000000000001</v>
@@ -15097,13 +15097,13 @@
         <v>0</v>
       </c>
       <c r="F24" s="189" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G24" s="118"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B25" s="180">
         <v>0.16500000000000001</v>
@@ -15118,12 +15118,12 @@
         <v>6.5883999999999998E-2</v>
       </c>
       <c r="F25" s="179" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B26" s="180">
         <v>0.16500000000000001</v>
@@ -15138,7 +15138,7 @@
         <v>0.1</v>
       </c>
       <c r="F26" s="179" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -15158,12 +15158,12 @@
         <v>0.127</v>
       </c>
       <c r="F27" s="179" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B28" s="180">
         <v>0.16500000000000001</v>
@@ -15178,12 +15178,12 @@
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="F28" s="179" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B29" s="180">
         <v>0.27500000000000002</v>
@@ -15192,12 +15192,12 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="F29" s="179" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B30" s="180">
         <v>1</v>
@@ -15212,12 +15212,12 @@
         <v>9.1097999999999998E-2</v>
       </c>
       <c r="F30" s="179" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B31" s="180">
         <v>0.16500000000000001</v>
@@ -15232,12 +15232,12 @@
         <v>0.122505</v>
       </c>
       <c r="F31" s="179" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B32" s="180">
         <v>0.27500000000000002</v>
@@ -15252,7 +15252,7 @@
         <v>0.140677</v>
       </c>
       <c r="F32" s="179" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -15272,7 +15272,7 @@
         <v>9.6627000000000005E-2</v>
       </c>
       <c r="F33" s="179" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -15292,7 +15292,7 @@
         <v>0.14300099999999999</v>
       </c>
       <c r="F34" s="179" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -15312,7 +15312,7 @@
         <v>9.2302999999999996E-2</v>
       </c>
       <c r="F35" s="179" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -15332,7 +15332,7 @@
         <v>0.13450899999999999</v>
       </c>
       <c r="F36" s="179" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -15352,12 +15352,12 @@
         <v>0.34243699999999999</v>
       </c>
       <c r="F37" s="179" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B38" s="180">
         <v>0.27500000000000002</v>
@@ -15366,12 +15366,12 @@
         <v>8.0000000000000004E-4</v>
       </c>
       <c r="F38" s="179" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B39" s="180">
         <v>0.16500000000000001</v>
@@ -15386,7 +15386,7 @@
         <v>0.20618</v>
       </c>
       <c r="F39" s="179" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -15406,7 +15406,7 @@
         <v>0.34920000000000001</v>
       </c>
       <c r="F40" s="179" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -15426,7 +15426,7 @@
         <v>0.214</v>
       </c>
       <c r="F41" s="179" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -15446,12 +15446,12 @@
         <v>0.15989999999999999</v>
       </c>
       <c r="F42" s="179" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B43" s="180">
         <v>1</v>
@@ -15466,7 +15466,7 @@
         <v>0.3105</v>
       </c>
       <c r="F43" s="179" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -15486,12 +15486,12 @@
         <v>0.14169999999999999</v>
       </c>
       <c r="F44" s="179" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B45" s="180">
         <v>0.1002</v>
@@ -15506,12 +15506,12 @@
         <v>0.2626</v>
       </c>
       <c r="F45" s="179" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B46" s="180">
         <v>0.16500000000000001</v>
@@ -15526,7 +15526,7 @@
         <v>0.31519999999999998</v>
       </c>
       <c r="F46" s="179" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>

--- a/spreadsheets/2026 Fin Inst Database.xlsx
+++ b/spreadsheets/2026 Fin Inst Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micha\git-projects\trading\spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{053DF81D-0030-4278-8F2A-6CCFDB258520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB7437DA-860D-48B7-99AA-93FA5CB215FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31785" yWindow="1020" windowWidth="25965" windowHeight="12585" tabRatio="763" activeTab="2" xr2:uid="{80E421DC-2A5F-48BD-91BD-DB367A6ED94D}"/>
+    <workbookView xWindow="1545" yWindow="1875" windowWidth="25965" windowHeight="12585" tabRatio="763" firstSheet="3" activeTab="3" xr2:uid="{80E421DC-2A5F-48BD-91BD-DB367A6ED94D}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="31" r:id="rId1"/>
@@ -1874,7 +1874,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="232">
+  <cellXfs count="231">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2439,15 +2439,6 @@
     <xf numFmtId="173" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="173" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2460,7 +2451,15 @@
     <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -14979,7 +14978,7 @@
     <col min="4" max="4" width="16.42578125" style="172" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.5703125" style="153" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27.5703125" style="155" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" style="225" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" style="222" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23" style="196" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.85546875" style="211" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23" style="196" bestFit="1" customWidth="1"/>
@@ -15022,7 +15021,7 @@
       <c r="F1" s="189" t="s">
         <v>297</v>
       </c>
-      <c r="G1" s="225" t="s">
+      <c r="G1" s="222" t="s">
         <v>455</v>
       </c>
       <c r="H1" s="211" t="s">
@@ -15108,7 +15107,7 @@
       <c r="F2" s="152">
         <v>651000</v>
       </c>
-      <c r="G2" s="226">
+      <c r="G2" s="223">
         <v>0.1</v>
       </c>
       <c r="H2" s="211">
@@ -15188,7 +15187,7 @@
       <c r="F3" s="152">
         <v>9160000</v>
       </c>
-      <c r="G3" s="226">
+      <c r="G3" s="223">
         <v>0.33710000000000001</v>
       </c>
       <c r="H3" s="211">
@@ -15268,7 +15267,7 @@
       <c r="F4" s="152">
         <v>481000</v>
       </c>
-      <c r="G4" s="226">
+      <c r="G4" s="223">
         <v>0.143787</v>
       </c>
       <c r="H4" s="211">
@@ -15348,7 +15347,7 @@
       <c r="F5" s="152">
         <v>777000</v>
       </c>
-      <c r="G5" s="226">
+      <c r="G5" s="223">
         <v>0.134461</v>
       </c>
       <c r="H5" s="211">
@@ -15428,7 +15427,7 @@
       <c r="F6" s="152">
         <v>2460000</v>
       </c>
-      <c r="G6" s="226">
+      <c r="G6" s="223">
         <v>0.20414599999999999</v>
       </c>
       <c r="H6" s="211">
@@ -15508,7 +15507,7 @@
       <c r="F7" s="152">
         <v>8170000</v>
       </c>
-      <c r="G7" s="226">
+      <c r="G7" s="223">
         <v>0.41367700000000002</v>
       </c>
       <c r="H7" s="211">
@@ -15588,7 +15587,7 @@
       <c r="F8" s="152">
         <v>1120000</v>
       </c>
-      <c r="G8" s="226">
+      <c r="G8" s="223">
         <v>0.14246</v>
       </c>
       <c r="H8" s="211">
@@ -15668,7 +15667,7 @@
       <c r="F9" s="152">
         <v>41300000</v>
       </c>
-      <c r="G9" s="226">
+      <c r="G9" s="223">
         <v>0.435025</v>
       </c>
       <c r="H9" s="211">
@@ -15748,7 +15747,7 @@
       <c r="F10" s="152">
         <v>13550000</v>
       </c>
-      <c r="G10" s="226">
+      <c r="G10" s="223">
         <v>0.21326600000000001</v>
       </c>
       <c r="H10" s="211">
@@ -15828,7 +15827,7 @@
       <c r="F11" s="152">
         <v>1540000</v>
       </c>
-      <c r="G11" s="226">
+      <c r="G11" s="223">
         <v>0</v>
       </c>
       <c r="H11" s="212">
@@ -15908,7 +15907,7 @@
       <c r="F12" s="152">
         <v>384000</v>
       </c>
-      <c r="G12" s="226">
+      <c r="G12" s="223">
         <v>0</v>
       </c>
       <c r="H12" s="212">
@@ -15988,7 +15987,7 @@
       <c r="F13" s="152">
         <v>1850000</v>
       </c>
-      <c r="G13" s="226">
+      <c r="G13" s="223">
         <v>0.21920000000000001</v>
       </c>
       <c r="H13" s="211">
@@ -16068,7 +16067,7 @@
       <c r="F14" s="152">
         <v>2490000</v>
       </c>
-      <c r="G14" s="226">
+      <c r="G14" s="223">
         <v>0.338841</v>
       </c>
       <c r="H14" s="211">
@@ -16148,7 +16147,7 @@
       <c r="F15" s="152">
         <v>3800000</v>
       </c>
-      <c r="G15" s="226">
+      <c r="G15" s="223">
         <v>0.28987299999999999</v>
       </c>
       <c r="H15" s="211">
@@ -16228,7 +16227,7 @@
       <c r="F16" s="152">
         <v>3230000</v>
       </c>
-      <c r="G16" s="226">
+      <c r="G16" s="223">
         <v>0.14724200000000001</v>
       </c>
       <c r="H16" s="211">
@@ -16308,7 +16307,9 @@
       <c r="F17" s="152">
         <v>107000</v>
       </c>
-      <c r="G17" s="231"/>
+      <c r="G17" s="223">
+        <v>0.39</v>
+      </c>
       <c r="H17" s="211">
         <v>46266</v>
       </c>
@@ -16386,7 +16387,7 @@
       <c r="F18" s="152">
         <v>2140000</v>
       </c>
-      <c r="G18" s="226">
+      <c r="G18" s="223">
         <v>7.6600000000000001E-2</v>
       </c>
       <c r="H18" s="211">
@@ -16466,7 +16467,7 @@
       <c r="F19" s="152">
         <v>1180000</v>
       </c>
-      <c r="G19" s="226">
+      <c r="G19" s="223">
         <v>0.1396</v>
       </c>
       <c r="H19" s="211">
@@ -16546,7 +16547,7 @@
       <c r="F20" s="152">
         <v>760000</v>
       </c>
-      <c r="G20" s="226">
+      <c r="G20" s="223">
         <v>0.10929999999999999</v>
       </c>
       <c r="H20" s="211">
@@ -16626,7 +16627,7 @@
       <c r="F21" s="152">
         <v>3320000</v>
       </c>
-      <c r="G21" s="226">
+      <c r="G21" s="223">
         <v>8.9305999999999996E-2</v>
       </c>
       <c r="H21" s="211">
@@ -16707,7 +16708,7 @@
       <c r="F22" s="152">
         <v>968000</v>
       </c>
-      <c r="G22" s="226">
+      <c r="G22" s="223">
         <v>0.154807</v>
       </c>
       <c r="H22" s="211">
@@ -16787,7 +16788,7 @@
       <c r="F23" s="152">
         <v>628000</v>
       </c>
-      <c r="G23" s="226">
+      <c r="G23" s="223">
         <v>0.123783</v>
       </c>
       <c r="H23" s="211">
@@ -16867,7 +16868,7 @@
       <c r="F24" s="152">
         <v>2800000</v>
       </c>
-      <c r="G24" s="226">
+      <c r="G24" s="223">
         <v>0.53229499999999996</v>
       </c>
       <c r="H24" s="211">
@@ -16948,7 +16949,7 @@
       <c r="F25" s="152">
         <v>5830000</v>
       </c>
-      <c r="G25" s="226">
+      <c r="G25" s="223">
         <v>0.14036100000000001</v>
       </c>
       <c r="H25" s="211">
@@ -17028,7 +17029,7 @@
       <c r="F26" s="152">
         <v>341000</v>
       </c>
-      <c r="G26" s="226">
+      <c r="G26" s="223">
         <v>4.4215999999999998E-2</v>
       </c>
       <c r="H26" s="211">
@@ -17108,7 +17109,7 @@
       <c r="F27" s="152">
         <v>4040000</v>
       </c>
-      <c r="G27" s="226">
+      <c r="G27" s="223">
         <v>0.10195799999999999</v>
       </c>
       <c r="H27" s="211">
@@ -17188,7 +17189,7 @@
       <c r="F28" s="152">
         <v>6500000</v>
       </c>
-      <c r="G28" s="226">
+      <c r="G28" s="223">
         <v>9.3530000000000002E-2</v>
       </c>
       <c r="H28" s="211">
@@ -17268,7 +17269,7 @@
       <c r="F29" s="152">
         <v>1030000</v>
       </c>
-      <c r="G29" s="226">
+      <c r="G29" s="223">
         <v>7.1248000000000006E-2</v>
       </c>
       <c r="H29" s="211">
@@ -17348,7 +17349,7 @@
       <c r="F30" s="152">
         <v>469000</v>
       </c>
-      <c r="G30" s="226">
+      <c r="G30" s="223">
         <v>0.13560700000000001</v>
       </c>
       <c r="H30" s="211">
@@ -17428,7 +17429,7 @@
       <c r="F31" s="152">
         <v>872000</v>
       </c>
-      <c r="G31" s="226">
+      <c r="G31" s="223">
         <v>0.159</v>
       </c>
       <c r="H31" s="211">
@@ -17508,7 +17509,7 @@
       <c r="F32" s="152">
         <v>8690000</v>
       </c>
-      <c r="G32" s="226">
+      <c r="G32" s="223">
         <v>0.252886</v>
       </c>
       <c r="H32" s="211">
@@ -17588,7 +17589,7 @@
       <c r="F33" s="152">
         <v>286000</v>
       </c>
-      <c r="G33" s="226">
+      <c r="G33" s="223">
         <v>0.26019999999999999</v>
       </c>
       <c r="H33" s="211">
@@ -17668,7 +17669,7 @@
       <c r="F34" s="152">
         <v>104000</v>
       </c>
-      <c r="G34" s="226">
+      <c r="G34" s="223">
         <v>0.32729999999999998</v>
       </c>
       <c r="H34" s="211">
@@ -17748,7 +17749,7 @@
       <c r="F35" s="152">
         <v>650000</v>
       </c>
-      <c r="G35" s="226">
+      <c r="G35" s="223">
         <v>0.32069999999999999</v>
       </c>
       <c r="H35" s="211">
@@ -17828,7 +17829,7 @@
       <c r="F36" s="152">
         <v>5160000</v>
       </c>
-      <c r="G36" s="226">
+      <c r="G36" s="223">
         <v>0.1206</v>
       </c>
       <c r="H36" s="211">
@@ -17908,7 +17909,7 @@
       <c r="F37" s="152">
         <v>5330000</v>
       </c>
-      <c r="G37" s="226">
+      <c r="G37" s="223">
         <v>0.36149999999999999</v>
       </c>
       <c r="H37" s="211">
@@ -17989,7 +17990,7 @@
       <c r="F38" s="152">
         <v>3000000</v>
       </c>
-      <c r="G38" s="226">
+      <c r="G38" s="223">
         <v>0.21529999999999999</v>
       </c>
       <c r="H38" s="211">
@@ -18069,7 +18070,7 @@
       <c r="F39" s="152">
         <v>1570000</v>
       </c>
-      <c r="G39" s="226">
+      <c r="G39" s="223">
         <v>0.1666</v>
       </c>
       <c r="H39" s="211">
@@ -18149,7 +18150,7 @@
       <c r="F40" s="152">
         <v>7560000</v>
       </c>
-      <c r="G40" s="226">
+      <c r="G40" s="223">
         <v>0.1434</v>
       </c>
       <c r="H40" s="211">
@@ -18229,7 +18230,7 @@
       <c r="F41" s="152">
         <v>1530000</v>
       </c>
-      <c r="G41" s="226">
+      <c r="G41" s="223">
         <v>0.19292999999999999</v>
       </c>
       <c r="H41" s="211">
@@ -20884,7 +20885,7 @@
         <v>3.0999999999999999E-3</v>
       </c>
       <c r="F77" s="186"/>
-      <c r="G77" s="227" t="s">
+      <c r="G77" s="224" t="s">
         <v>315</v>
       </c>
       <c r="H77" s="211"/>
@@ -20913,7 +20914,7 @@
         <v>5.9999999999999995E-4</v>
       </c>
       <c r="F78" s="186"/>
-      <c r="G78" s="227"/>
+      <c r="G78" s="224"/>
       <c r="H78" s="211"/>
       <c r="J78" s="211"/>
       <c r="L78" s="211"/>
@@ -20940,7 +20941,7 @@
         <v>1.4E-3</v>
       </c>
       <c r="F79" s="186"/>
-      <c r="G79" s="227"/>
+      <c r="G79" s="224"/>
       <c r="H79" s="211"/>
       <c r="J79" s="211"/>
       <c r="L79" s="211"/>
@@ -20967,7 +20968,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="F80" s="186"/>
-      <c r="G80" s="227" t="s">
+      <c r="G80" s="224" t="s">
         <v>387</v>
       </c>
       <c r="H80" s="211"/>
@@ -20996,7 +20997,7 @@
         <v>1.5E-3</v>
       </c>
       <c r="F81" s="186"/>
-      <c r="G81" s="227" t="s">
+      <c r="G81" s="224" t="s">
         <v>384</v>
       </c>
       <c r="H81" s="211"/>
@@ -21011,7 +21012,7 @@
       <c r="Z81" s="211"/>
     </row>
     <row r="82" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G82" s="228"/>
+      <c r="G82" s="225"/>
       <c r="H82" s="211"/>
       <c r="J82" s="211"/>
       <c r="L82" s="211"/>
@@ -21038,7 +21039,7 @@
       <c r="F83" s="192">
         <v>91200</v>
       </c>
-      <c r="G83" s="227" t="s">
+      <c r="G83" s="224" t="s">
         <v>309</v>
       </c>
       <c r="H83" s="211"/>
@@ -21067,7 +21068,7 @@
       <c r="F84" s="192">
         <v>7622971</v>
       </c>
-      <c r="G84" s="227" t="s">
+      <c r="G84" s="224" t="s">
         <v>315</v>
       </c>
       <c r="H84" s="211"/>
@@ -21082,7 +21083,7 @@
       <c r="Z84" s="211"/>
     </row>
     <row r="85" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G85" s="228"/>
+      <c r="G85" s="225"/>
       <c r="H85" s="211"/>
       <c r="J85" s="211"/>
       <c r="L85" s="211"/>
@@ -21109,7 +21110,7 @@
       <c r="F86" s="192">
         <v>85957</v>
       </c>
-      <c r="G86" s="227" t="s">
+      <c r="G86" s="224" t="s">
         <v>304</v>
       </c>
       <c r="H86" s="211"/>
@@ -21138,7 +21139,7 @@
       <c r="F87" s="192">
         <v>56587</v>
       </c>
-      <c r="G87" s="227" t="s">
+      <c r="G87" s="224" t="s">
         <v>304</v>
       </c>
       <c r="H87" s="211"/>
@@ -21171,7 +21172,7 @@
       <c r="D89" s="14"/>
       <c r="E89" s="14"/>
       <c r="F89" s="14"/>
-      <c r="G89" s="229"/>
+      <c r="G89" s="226"/>
       <c r="H89" s="216"/>
       <c r="I89" s="216"/>
       <c r="J89" s="216"/>
@@ -21197,7 +21198,7 @@
       <c r="D90" s="14"/>
       <c r="E90" s="14"/>
       <c r="F90" s="14"/>
-      <c r="G90" s="229"/>
+      <c r="G90" s="226"/>
       <c r="H90" s="216"/>
       <c r="I90" s="216"/>
       <c r="J90" s="216"/>
@@ -21223,7 +21224,7 @@
       <c r="D91" s="14"/>
       <c r="E91" s="14"/>
       <c r="F91" s="14"/>
-      <c r="G91" s="229"/>
+      <c r="G91" s="226"/>
       <c r="H91" s="219"/>
       <c r="I91" s="216"/>
       <c r="J91" s="219"/>
@@ -21245,7 +21246,7 @@
       <c r="D92" s="14"/>
       <c r="E92" s="14"/>
       <c r="F92" s="14"/>
-      <c r="G92" s="229"/>
+      <c r="G92" s="226"/>
       <c r="H92" s="219"/>
       <c r="I92" s="216"/>
       <c r="J92" s="219"/>
@@ -21267,7 +21268,7 @@
       <c r="D93" s="14"/>
       <c r="E93" s="14"/>
       <c r="F93" s="14"/>
-      <c r="G93" s="229"/>
+      <c r="G93" s="226"/>
       <c r="H93" s="219"/>
       <c r="I93" s="216"/>
       <c r="J93" s="219"/>
@@ -21289,7 +21290,7 @@
       <c r="D94" s="14"/>
       <c r="E94" s="154"/>
       <c r="F94" s="153"/>
-      <c r="G94" s="229"/>
+      <c r="G94" s="226"/>
       <c r="H94" s="220"/>
       <c r="I94" s="216"/>
       <c r="J94" s="220"/>
@@ -21311,7 +21312,7 @@
       <c r="D95" s="14"/>
       <c r="E95" s="154"/>
       <c r="F95" s="153"/>
-      <c r="G95" s="229"/>
+      <c r="G95" s="226"/>
       <c r="H95" s="220"/>
       <c r="I95" s="216"/>
       <c r="J95" s="220"/>
@@ -21333,7 +21334,7 @@
       <c r="D96" s="14"/>
       <c r="E96" s="154"/>
       <c r="F96" s="153"/>
-      <c r="G96" s="229"/>
+      <c r="G96" s="226"/>
       <c r="H96" s="220"/>
       <c r="I96" s="216"/>
       <c r="J96" s="220"/>
@@ -21355,7 +21356,7 @@
       <c r="D97" s="14"/>
       <c r="E97" s="154"/>
       <c r="F97" s="153"/>
-      <c r="G97" s="229"/>
+      <c r="G97" s="226"/>
       <c r="H97" s="220"/>
       <c r="I97" s="216"/>
       <c r="J97" s="220"/>
@@ -21377,7 +21378,7 @@
       <c r="D98" s="14"/>
       <c r="E98" s="154"/>
       <c r="F98" s="153"/>
-      <c r="G98" s="229"/>
+      <c r="G98" s="226"/>
       <c r="H98" s="220"/>
       <c r="I98" s="216"/>
       <c r="J98" s="220"/>
@@ -21399,7 +21400,7 @@
       <c r="D99" s="14"/>
       <c r="E99" s="154"/>
       <c r="F99" s="153"/>
-      <c r="G99" s="229"/>
+      <c r="G99" s="226"/>
       <c r="H99" s="220"/>
       <c r="I99" s="216"/>
       <c r="J99" s="220"/>
@@ -21421,7 +21422,7 @@
       <c r="D100" s="14"/>
       <c r="E100" s="154"/>
       <c r="F100" s="153"/>
-      <c r="G100" s="229"/>
+      <c r="G100" s="226"/>
       <c r="H100" s="220"/>
       <c r="I100" s="216"/>
       <c r="J100" s="220"/>
@@ -21443,7 +21444,7 @@
       <c r="D101" s="14"/>
       <c r="E101" s="154"/>
       <c r="F101" s="153"/>
-      <c r="G101" s="230"/>
+      <c r="G101" s="227"/>
       <c r="H101" s="188"/>
       <c r="I101" s="215"/>
       <c r="J101" s="188"/>
@@ -21465,7 +21466,7 @@
       <c r="D102" s="14"/>
       <c r="E102" s="154"/>
       <c r="F102" s="153"/>
-      <c r="G102" s="230"/>
+      <c r="G102" s="227"/>
       <c r="H102" s="188"/>
       <c r="I102" s="215"/>
       <c r="J102" s="188"/>
@@ -21487,7 +21488,7 @@
       <c r="D103" s="14"/>
       <c r="E103" s="154"/>
       <c r="F103" s="153"/>
-      <c r="G103" s="230"/>
+      <c r="G103" s="227"/>
       <c r="H103" s="188"/>
       <c r="I103" s="215"/>
       <c r="J103" s="188"/>
@@ -21509,7 +21510,7 @@
       <c r="D104" s="14"/>
       <c r="E104" s="154"/>
       <c r="F104" s="153"/>
-      <c r="G104" s="230"/>
+      <c r="G104" s="227"/>
       <c r="H104" s="188"/>
       <c r="I104" s="215"/>
       <c r="J104" s="188"/>
@@ -21531,7 +21532,7 @@
       <c r="D105" s="14"/>
       <c r="E105" s="154"/>
       <c r="F105" s="153"/>
-      <c r="G105" s="230"/>
+      <c r="G105" s="227"/>
       <c r="H105" s="188"/>
       <c r="I105" s="215"/>
       <c r="J105" s="188"/>
@@ -21553,7 +21554,7 @@
       <c r="D106" s="14"/>
       <c r="E106" s="154"/>
       <c r="F106" s="153"/>
-      <c r="G106" s="230"/>
+      <c r="G106" s="227"/>
       <c r="H106" s="188"/>
       <c r="I106" s="215"/>
       <c r="J106" s="188"/>
@@ -21575,7 +21576,7 @@
       <c r="D107" s="14"/>
       <c r="E107" s="154"/>
       <c r="F107" s="153"/>
-      <c r="G107" s="230"/>
+      <c r="G107" s="227"/>
       <c r="H107" s="188"/>
       <c r="I107" s="215"/>
       <c r="J107" s="188"/>
@@ -21597,7 +21598,7 @@
       <c r="D108" s="14"/>
       <c r="E108" s="154"/>
       <c r="F108" s="153"/>
-      <c r="G108" s="230"/>
+      <c r="G108" s="227"/>
       <c r="H108" s="188"/>
       <c r="I108" s="215"/>
       <c r="J108" s="188"/>
@@ -21619,7 +21620,7 @@
       <c r="D109" s="14"/>
       <c r="E109" s="154"/>
       <c r="F109" s="153"/>
-      <c r="G109" s="230"/>
+      <c r="G109" s="227"/>
       <c r="H109" s="188"/>
       <c r="I109" s="215"/>
       <c r="J109" s="188"/>
@@ -21641,7 +21642,7 @@
       <c r="D110" s="14"/>
       <c r="E110" s="154"/>
       <c r="F110" s="153"/>
-      <c r="G110" s="230"/>
+      <c r="G110" s="227"/>
       <c r="H110" s="188"/>
       <c r="I110" s="215"/>
       <c r="J110" s="188"/>
@@ -21663,7 +21664,7 @@
       <c r="D111" s="14"/>
       <c r="E111" s="154"/>
       <c r="F111" s="153"/>
-      <c r="G111" s="230"/>
+      <c r="G111" s="227"/>
       <c r="H111" s="188"/>
       <c r="I111" s="215"/>
       <c r="J111" s="188"/>
@@ -21685,7 +21686,7 @@
       <c r="D112" s="14"/>
       <c r="E112" s="154"/>
       <c r="F112" s="153"/>
-      <c r="G112" s="230"/>
+      <c r="G112" s="227"/>
       <c r="H112" s="188"/>
       <c r="I112" s="215"/>
       <c r="J112" s="188"/>
@@ -21707,7 +21708,7 @@
       <c r="D113" s="14"/>
       <c r="E113" s="154"/>
       <c r="F113" s="153"/>
-      <c r="G113" s="230"/>
+      <c r="G113" s="227"/>
       <c r="H113" s="188"/>
       <c r="I113" s="215"/>
       <c r="J113" s="188"/>
@@ -21729,7 +21730,7 @@
       <c r="D114" s="14"/>
       <c r="E114" s="154"/>
       <c r="F114" s="153"/>
-      <c r="G114" s="230"/>
+      <c r="G114" s="227"/>
       <c r="H114" s="188"/>
       <c r="I114" s="215"/>
       <c r="J114" s="188"/>
@@ -21751,7 +21752,7 @@
       <c r="D115" s="14"/>
       <c r="E115" s="154"/>
       <c r="F115" s="153"/>
-      <c r="G115" s="230"/>
+      <c r="G115" s="227"/>
       <c r="H115" s="188"/>
       <c r="I115" s="215"/>
       <c r="J115" s="188"/>
@@ -21773,7 +21774,7 @@
       <c r="D116" s="14"/>
       <c r="E116" s="154"/>
       <c r="F116" s="153"/>
-      <c r="G116" s="230"/>
+      <c r="G116" s="227"/>
       <c r="H116" s="188"/>
       <c r="I116" s="215"/>
       <c r="J116" s="188"/>
@@ -21795,7 +21796,7 @@
       <c r="D117" s="14"/>
       <c r="E117" s="154"/>
       <c r="F117" s="153"/>
-      <c r="G117" s="230"/>
+      <c r="G117" s="227"/>
       <c r="H117" s="188"/>
       <c r="I117" s="215"/>
       <c r="J117" s="188"/>
@@ -21817,7 +21818,7 @@
       <c r="D118" s="14"/>
       <c r="E118" s="154"/>
       <c r="F118" s="153"/>
-      <c r="G118" s="230"/>
+      <c r="G118" s="227"/>
       <c r="H118" s="188"/>
       <c r="I118" s="215"/>
       <c r="J118" s="188"/>
@@ -21839,7 +21840,7 @@
       <c r="D119" s="14"/>
       <c r="E119" s="154"/>
       <c r="F119" s="153"/>
-      <c r="G119" s="230"/>
+      <c r="G119" s="227"/>
       <c r="H119" s="188"/>
       <c r="I119" s="215"/>
       <c r="J119" s="188"/>
@@ -21861,7 +21862,7 @@
       <c r="D120" s="14"/>
       <c r="E120" s="154"/>
       <c r="F120" s="153"/>
-      <c r="G120" s="230"/>
+      <c r="G120" s="227"/>
       <c r="H120" s="188"/>
       <c r="I120" s="215"/>
       <c r="J120" s="188"/>
@@ -21883,7 +21884,7 @@
       <c r="D121" s="14"/>
       <c r="E121" s="154"/>
       <c r="F121" s="153"/>
-      <c r="G121" s="230"/>
+      <c r="G121" s="227"/>
       <c r="H121" s="188"/>
       <c r="I121" s="215"/>
       <c r="J121" s="188"/>
@@ -21905,7 +21906,7 @@
       <c r="D122" s="14"/>
       <c r="E122" s="154"/>
       <c r="F122" s="153"/>
-      <c r="G122" s="230"/>
+      <c r="G122" s="227"/>
       <c r="H122" s="188"/>
       <c r="I122" s="215"/>
       <c r="J122" s="188"/>
@@ -21927,7 +21928,7 @@
       <c r="D123" s="14"/>
       <c r="E123" s="154"/>
       <c r="F123" s="153"/>
-      <c r="G123" s="230"/>
+      <c r="G123" s="227"/>
       <c r="H123" s="188"/>
       <c r="I123" s="215"/>
       <c r="J123" s="188"/>
@@ -21949,7 +21950,7 @@
       <c r="D124" s="14"/>
       <c r="E124" s="154"/>
       <c r="F124" s="153"/>
-      <c r="G124" s="230"/>
+      <c r="G124" s="227"/>
       <c r="H124" s="188"/>
       <c r="I124" s="215"/>
       <c r="J124" s="188"/>
@@ -21971,7 +21972,7 @@
       <c r="D125" s="14"/>
       <c r="E125" s="154"/>
       <c r="F125" s="153"/>
-      <c r="G125" s="230"/>
+      <c r="G125" s="227"/>
       <c r="H125" s="188"/>
       <c r="I125" s="215"/>
       <c r="J125" s="188"/>
@@ -21993,7 +21994,7 @@
       <c r="D126" s="14"/>
       <c r="E126" s="154"/>
       <c r="F126" s="153"/>
-      <c r="G126" s="230"/>
+      <c r="G126" s="227"/>
       <c r="H126" s="188"/>
       <c r="I126" s="215"/>
       <c r="J126" s="188"/>
@@ -22015,7 +22016,7 @@
       <c r="D127" s="14"/>
       <c r="E127" s="154"/>
       <c r="F127" s="153"/>
-      <c r="G127" s="230"/>
+      <c r="G127" s="227"/>
       <c r="H127" s="188"/>
       <c r="I127" s="215"/>
       <c r="J127" s="188"/>
@@ -22037,7 +22038,7 @@
       <c r="D128" s="14"/>
       <c r="E128" s="154"/>
       <c r="F128" s="153"/>
-      <c r="G128" s="230"/>
+      <c r="G128" s="227"/>
       <c r="H128" s="188"/>
       <c r="I128" s="215"/>
       <c r="J128" s="188"/>
@@ -26002,7 +26003,7 @@
       </c>
       <c r="D5" s="160" t="str">
         <f ca="1">_xlfn.CONCAT("ETF_",D15,".csv")</f>
-        <v>ETF_2026-09-01.csv</v>
+        <v>ETF_2026-09-02.csv</v>
       </c>
       <c r="E5" s="146"/>
     </row>
@@ -26131,7 +26132,7 @@
     <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D15" s="164" t="str">
         <f t="shared" ref="D15" ca="1" si="0">TEXT(TODAY(),"yyyy-mm-dd")</f>
-        <v>2026-09-01</v>
+        <v>2026-09-02</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -26809,29 +26810,29 @@
       <c r="C1" s="69" t="s">
         <v>174</v>
       </c>
-      <c r="D1" s="222" t="s">
+      <c r="D1" s="228" t="s">
         <v>199</v>
       </c>
-      <c r="E1" s="223"/>
-      <c r="F1" s="223"/>
-      <c r="G1" s="223"/>
-      <c r="H1" s="222" t="s">
+      <c r="E1" s="229"/>
+      <c r="F1" s="229"/>
+      <c r="G1" s="229"/>
+      <c r="H1" s="228" t="s">
         <v>200</v>
       </c>
-      <c r="I1" s="223"/>
-      <c r="J1" s="223"/>
-      <c r="K1" s="222" t="s">
+      <c r="I1" s="229"/>
+      <c r="J1" s="229"/>
+      <c r="K1" s="228" t="s">
         <v>204</v>
       </c>
-      <c r="L1" s="223"/>
-      <c r="M1" s="223"/>
-      <c r="N1" s="224"/>
-      <c r="O1" s="222" t="s">
+      <c r="L1" s="229"/>
+      <c r="M1" s="229"/>
+      <c r="N1" s="230"/>
+      <c r="O1" s="228" t="s">
         <v>205</v>
       </c>
-      <c r="P1" s="223"/>
-      <c r="Q1" s="223"/>
-      <c r="R1" s="224"/>
+      <c r="P1" s="229"/>
+      <c r="Q1" s="229"/>
+      <c r="R1" s="230"/>
     </row>
     <row r="2" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="106" t="s">

--- a/spreadsheets/2026 Fin Inst Database.xlsx
+++ b/spreadsheets/2026 Fin Inst Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micha\git-projects\trading\spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB7437DA-860D-48B7-99AA-93FA5CB215FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762CF3FD-F35C-4BD3-8F9F-6811EA709E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1545" yWindow="1875" windowWidth="25965" windowHeight="12585" tabRatio="763" firstSheet="3" activeTab="3" xr2:uid="{80E421DC-2A5F-48BD-91BD-DB367A6ED94D}"/>
+    <workbookView xWindow="30510" yWindow="2610" windowWidth="20265" windowHeight="9765" tabRatio="763" firstSheet="3" activeTab="3" xr2:uid="{80E421DC-2A5F-48BD-91BD-DB367A6ED94D}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="31" r:id="rId1"/>
@@ -2610,11 +2610,31 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
         <family val="2"/>
-        <scheme val="none"/>
+        <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="172" formatCode="_(&quot;$&quot;* #,##0.000000_);_(&quot;$&quot;* \(#,##0.000000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2629,11 +2649,32 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
         <family val="2"/>
-        <scheme val="none"/>
+        <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="173" formatCode="_(&quot;$&quot;* #,##0.00000_);_(&quot;$&quot;* \(#,##0.00000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2648,16 +2689,17 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
         <family val="2"/>
-        <scheme val="none"/>
+        <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="173" formatCode="_(&quot;$&quot;* #,##0.00000_);_(&quot;$&quot;* \(#,##0.00000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -2667,12 +2709,315 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color auto="1"/>
-        <name val="Arial"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
         <family val="2"/>
-        <scheme val="none"/>
+        <scheme val="minor"/>
       </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="173" formatCode="_(&quot;$&quot;* #,##0.00000_);_(&quot;$&quot;* \(#,##0.00000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="173" formatCode="_(&quot;$&quot;* #,##0.00000_);_(&quot;$&quot;* \(#,##0.00000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="173" formatCode="_(&quot;$&quot;* #,##0.00000_);_(&quot;$&quot;* \(#,##0.00000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="173" formatCode="_(&quot;$&quot;* #,##0.00000_);_(&quot;$&quot;* \(#,##0.00000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="173" formatCode="_(&quot;$&quot;* #,##0.00000_);_(&quot;$&quot;* \(#,##0.00000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="173" formatCode="_(&quot;$&quot;* #,##0.00000_);_(&quot;$&quot;* \(#,##0.00000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="173" formatCode="_(&quot;$&quot;* #,##0.00000_);_(&quot;$&quot;* \(#,##0.00000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="173" formatCode="_(&quot;$&quot;* #,##0.00000_);_(&quot;$&quot;* \(#,##0.00000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <font>
@@ -2687,15 +3032,21 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
         <color auto="1"/>
-        <name val="Arial"/>
+        <name val="Aptos Narrow"/>
         <family val="2"/>
-        <scheme val="none"/>
+        <scheme val="minor"/>
       </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
+        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -2706,9 +3057,16 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
         <color theme="1"/>
-        <name val="Arial"/>
+        <name val="Aptos Narrow"/>
         <family val="2"/>
-        <scheme val="none"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
       </font>
     </dxf>
     <dxf>
@@ -3553,12 +3911,88 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
+        <color auto="1"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
       </font>
-      <numFmt numFmtId="172" formatCode="_(&quot;$&quot;* #,##0.000000_);_(&quot;$&quot;* \(#,##0.000000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3573,443 +4007,9 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
         <color theme="1"/>
-        <name val="Aptos Narrow"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="173" formatCode="_(&quot;$&quot;* #,##0.00000_);_(&quot;$&quot;* \(#,##0.00000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="173" formatCode="_(&quot;$&quot;* #,##0.00000_);_(&quot;$&quot;* \(#,##0.00000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="173" formatCode="_(&quot;$&quot;* #,##0.00000_);_(&quot;$&quot;* \(#,##0.00000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="173" formatCode="_(&quot;$&quot;* #,##0.00000_);_(&quot;$&quot;* \(#,##0.00000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="173" formatCode="_(&quot;$&quot;* #,##0.00000_);_(&quot;$&quot;* \(#,##0.00000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="173" formatCode="_(&quot;$&quot;* #,##0.00000_);_(&quot;$&quot;* \(#,##0.00000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="173" formatCode="_(&quot;$&quot;* #,##0.00000_);_(&quot;$&quot;* \(#,##0.00000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="173" formatCode="_(&quot;$&quot;* #,##0.00000_);_(&quot;$&quot;* \(#,##0.00000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="173" formatCode="_(&quot;$&quot;* #,##0.00000_);_(&quot;$&quot;* \(#,##0.00000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="173" formatCode="_(&quot;$&quot;* #,##0.00000_);_(&quot;$&quot;* \(#,##0.00000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <scheme val="none"/>
       </font>
     </dxf>
   </dxfs>
@@ -4026,34 +4026,34 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D0B1F78D-D1AA-4EF3-9596-7A27A355C060}" name="static_data_table" displayName="static_data_table" ref="A1:O152" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64" headerRowCellStyle="Comma" dataCellStyle="Comma">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D0B1F78D-D1AA-4EF3-9596-7A27A355C060}" name="static_data_table" displayName="static_data_table" ref="A1:O152" totalsRowShown="0" headerRowDxfId="84" dataDxfId="83" headerRowCellStyle="Comma" dataCellStyle="Comma">
   <autoFilter ref="A1:O152" xr:uid="{D0B1F78D-D1AA-4EF3-9596-7A27A355C060}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A118:O151">
     <sortCondition ref="B1:B152"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="19" xr3:uid="{1221CC04-A25D-42E0-9BD3-B46333797DBE}" name="vpn" dataDxfId="63" dataCellStyle="Comma"/>
-    <tableColumn id="10" xr3:uid="{BED55A9A-3E28-4A17-AA02-2381DB89A658}" name="group" dataDxfId="62" dataCellStyle="Comma"/>
-    <tableColumn id="12" xr3:uid="{F9B08B7F-16AE-460B-BDFB-B2726D177E92}" name="sector" dataDxfId="61" dataCellStyle="Comma"/>
-    <tableColumn id="1" xr3:uid="{8C59AB6B-6EBF-48B8-9D8A-4E9EFB96C425}" name="my_prod_type" dataDxfId="60"/>
-    <tableColumn id="18" xr3:uid="{D3CEE51C-FF16-474C-AC93-30CEB3E7D375}" name="my_fi_name" dataDxfId="59" dataCellStyle="Comma"/>
-    <tableColumn id="22" xr3:uid="{51F924B8-25BB-4080-AD58-7509A60E27B0}" name="my_pf_name" dataDxfId="58"/>
-    <tableColumn id="2" xr3:uid="{A13A7736-F17C-4146-B643-6EF65FC4B25C}" name="pf_locator" dataDxfId="57"/>
-    <tableColumn id="4" xr3:uid="{211C7B2F-2849-4B0F-B281-BF0424C5B57F}" name="top_currency" dataDxfId="56" dataCellStyle="Comma"/>
-    <tableColumn id="3" xr3:uid="{46C5F41D-D64D-4F76-9E5D-390D6FE03BE6}" name="base_currency" dataDxfId="55" dataCellStyle="Comma"/>
-    <tableColumn id="9" xr3:uid="{E2441BE5-ABB7-40CB-848F-02508F05A37C}" name="comm_type" dataDxfId="54" dataCellStyle="Comma"/>
-    <tableColumn id="5" xr3:uid="{16FCE019-989B-4467-A8B9-96A8E58B2A2A}" name="comm_maker" dataDxfId="53" dataCellStyle="Currency"/>
-    <tableColumn id="6" xr3:uid="{0E805949-D535-4626-85EB-FA3727E7DAF4}" name="comm_taker" dataDxfId="52" dataCellStyle="Currency"/>
-    <tableColumn id="7" xr3:uid="{5709324A-7C63-43F4-AF59-F119177A7972}" name="comm_misc" dataDxfId="51" dataCellStyle="Comma"/>
-    <tableColumn id="8" xr3:uid="{32E47B88-05FD-48EE-97A0-59BC78476043}" name="comm_update" dataDxfId="50" dataCellStyle="Comma"/>
-    <tableColumn id="11" xr3:uid="{B6578BCD-793E-47C9-99CF-D01D02E8D922}" name="mkt_data_stream" dataDxfId="49" dataCellStyle="Comma"/>
+    <tableColumn id="19" xr3:uid="{1221CC04-A25D-42E0-9BD3-B46333797DBE}" name="vpn" dataDxfId="82" dataCellStyle="Comma"/>
+    <tableColumn id="10" xr3:uid="{BED55A9A-3E28-4A17-AA02-2381DB89A658}" name="group" dataDxfId="81" dataCellStyle="Comma"/>
+    <tableColumn id="12" xr3:uid="{F9B08B7F-16AE-460B-BDFB-B2726D177E92}" name="sector" dataDxfId="80" dataCellStyle="Comma"/>
+    <tableColumn id="1" xr3:uid="{8C59AB6B-6EBF-48B8-9D8A-4E9EFB96C425}" name="my_prod_type" dataDxfId="79"/>
+    <tableColumn id="18" xr3:uid="{D3CEE51C-FF16-474C-AC93-30CEB3E7D375}" name="my_fi_name" dataDxfId="78" dataCellStyle="Comma"/>
+    <tableColumn id="22" xr3:uid="{51F924B8-25BB-4080-AD58-7509A60E27B0}" name="my_pf_name" dataDxfId="77"/>
+    <tableColumn id="2" xr3:uid="{A13A7736-F17C-4146-B643-6EF65FC4B25C}" name="pf_locator" dataDxfId="76"/>
+    <tableColumn id="4" xr3:uid="{211C7B2F-2849-4B0F-B281-BF0424C5B57F}" name="top_currency" dataDxfId="75" dataCellStyle="Comma"/>
+    <tableColumn id="3" xr3:uid="{46C5F41D-D64D-4F76-9E5D-390D6FE03BE6}" name="base_currency" dataDxfId="74" dataCellStyle="Comma"/>
+    <tableColumn id="9" xr3:uid="{E2441BE5-ABB7-40CB-848F-02508F05A37C}" name="comm_type" dataDxfId="73" dataCellStyle="Comma"/>
+    <tableColumn id="5" xr3:uid="{16FCE019-989B-4467-A8B9-96A8E58B2A2A}" name="comm_maker" dataDxfId="72" dataCellStyle="Currency"/>
+    <tableColumn id="6" xr3:uid="{0E805949-D535-4626-85EB-FA3727E7DAF4}" name="comm_taker" dataDxfId="71" dataCellStyle="Currency"/>
+    <tableColumn id="7" xr3:uid="{5709324A-7C63-43F4-AF59-F119177A7972}" name="comm_misc" dataDxfId="70" dataCellStyle="Comma"/>
+    <tableColumn id="8" xr3:uid="{32E47B88-05FD-48EE-97A0-59BC78476043}" name="comm_update" dataDxfId="69" dataCellStyle="Comma"/>
+    <tableColumn id="11" xr3:uid="{B6578BCD-793E-47C9-99CF-D01D02E8D922}" name="mkt_data_stream" dataDxfId="68" dataCellStyle="Comma"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{8AFBE59F-E145-48B4-A9F0-75F818F296F4}" name="btc_to_do" displayName="btc_to_do" ref="A157:AA210" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{8AFBE59F-E145-48B4-A9F0-75F818F296F4}" name="btc_to_do" displayName="btc_to_do" ref="A157:AA210" totalsRowShown="0" headerRowDxfId="67" dataDxfId="66">
   <autoFilter ref="A157:AA210" xr:uid="{8AFBE59F-E145-48B4-A9F0-75F818F296F4}">
     <filterColumn colId="1">
       <filters>
@@ -4062,33 +4062,33 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{73FD62E2-E8FE-4C00-9C3C-F3122EB55D0D}" name="Column1" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{F8F856BF-80BD-4398-8276-448953D1A283}" name="Column2" dataDxfId="45"/>
-    <tableColumn id="3" xr3:uid="{859FF76C-0D7F-496C-B885-2DE680F3F916}" name="Column7" dataDxfId="44"/>
-    <tableColumn id="4" xr3:uid="{EFE5B159-5688-4C13-A02D-A6C704275E2E}" name="Column4" dataDxfId="43"/>
-    <tableColumn id="5" xr3:uid="{69D00D15-DF82-46C9-9945-107A85371A6F}" name="Column5" dataDxfId="42"/>
-    <tableColumn id="6" xr3:uid="{F10DE59E-3B92-4DD0-8A04-FAE76E9F8BB9}" name="Column6" dataDxfId="41"/>
-    <tableColumn id="8" xr3:uid="{2D949549-0F5C-4A89-B8F7-72304B9A24F1}" name="Column8" dataDxfId="40"/>
-    <tableColumn id="9" xr3:uid="{C42826CE-029E-4945-8434-CBC9F4DAA57F}" name="Column9" dataDxfId="39" dataCellStyle="Comma"/>
-    <tableColumn id="7" xr3:uid="{F0789B57-A27F-47CD-94AE-4F6B71344DB9}" name="Column92" dataDxfId="38" dataCellStyle="Currency"/>
-    <tableColumn id="13" xr3:uid="{84F8B5AD-93FB-4C3E-8E09-FB358E10FC62}" name="Column93" dataDxfId="37" dataCellStyle="Currency"/>
-    <tableColumn id="14" xr3:uid="{DA8CB162-5C11-45A4-93E0-E0C45C3ED3D0}" name="Column94" dataDxfId="36" dataCellStyle="Comma"/>
-    <tableColumn id="27" xr3:uid="{100A9F62-6915-49BB-B014-4D0BC03BB553}" name="Column95" dataDxfId="35" dataCellStyle="Comma"/>
-    <tableColumn id="10" xr3:uid="{5B60D48A-2B91-4E81-AD9D-2709C1335F32}" name="Column10" dataDxfId="34" dataCellStyle="Comma"/>
-    <tableColumn id="11" xr3:uid="{E1B16D3B-DEA4-44A7-8DE4-CA3F41D77B2B}" name="Column11" dataDxfId="33" dataCellStyle="Comma"/>
-    <tableColumn id="12" xr3:uid="{793817C6-38BE-49BA-A9A6-4F96D87310D9}" name="Column12" dataDxfId="32" dataCellStyle="Comma"/>
-    <tableColumn id="15" xr3:uid="{2AFA675A-D2B0-476D-A865-BB72634DC6DA}" name="Column15" dataDxfId="31"/>
-    <tableColumn id="16" xr3:uid="{B5249436-7148-4EBF-B8E6-5226AA101320}" name="Column16" dataDxfId="30" dataCellStyle="Currency"/>
-    <tableColumn id="17" xr3:uid="{22140E2C-B2EC-4771-8D39-0E8FE9F80B88}" name="Column17" dataDxfId="29"/>
-    <tableColumn id="18" xr3:uid="{AC423A03-E794-4524-9C7D-D02B01892118}" name="Column18" dataDxfId="28" dataCellStyle="Comma"/>
-    <tableColumn id="19" xr3:uid="{F73A917A-F13B-4BB9-8524-E34E6050878C}" name="Column19" dataDxfId="27" dataCellStyle="Comma"/>
-    <tableColumn id="20" xr3:uid="{4A9B484B-EBD7-41D1-8470-161DB87D7FB2}" name="Column20" dataDxfId="26" dataCellStyle="Comma"/>
-    <tableColumn id="21" xr3:uid="{D03D1805-69BB-4D67-B61E-961F2E625E81}" name="Column21" dataDxfId="25"/>
-    <tableColumn id="22" xr3:uid="{66E8E4D1-FF14-404F-8354-025C93AED5CB}" name="Column22" dataDxfId="24"/>
-    <tableColumn id="23" xr3:uid="{9540F131-1C8F-4F4F-8796-92F1AFD57E03}" name="Column23" dataDxfId="23"/>
-    <tableColumn id="24" xr3:uid="{B7156378-CEA1-4808-9801-4E93C755FE92}" name="Column24" dataDxfId="22"/>
-    <tableColumn id="25" xr3:uid="{6908C233-AA1B-4818-BF8F-36FC13C53D09}" name="Column25" dataDxfId="21"/>
-    <tableColumn id="26" xr3:uid="{104781D6-1EEE-4947-A424-3CE3DCADF4CF}" name="Column26" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{73FD62E2-E8FE-4C00-9C3C-F3122EB55D0D}" name="Column1" dataDxfId="65"/>
+    <tableColumn id="2" xr3:uid="{F8F856BF-80BD-4398-8276-448953D1A283}" name="Column2" dataDxfId="64"/>
+    <tableColumn id="3" xr3:uid="{859FF76C-0D7F-496C-B885-2DE680F3F916}" name="Column7" dataDxfId="63"/>
+    <tableColumn id="4" xr3:uid="{EFE5B159-5688-4C13-A02D-A6C704275E2E}" name="Column4" dataDxfId="62"/>
+    <tableColumn id="5" xr3:uid="{69D00D15-DF82-46C9-9945-107A85371A6F}" name="Column5" dataDxfId="61"/>
+    <tableColumn id="6" xr3:uid="{F10DE59E-3B92-4DD0-8A04-FAE76E9F8BB9}" name="Column6" dataDxfId="60"/>
+    <tableColumn id="8" xr3:uid="{2D949549-0F5C-4A89-B8F7-72304B9A24F1}" name="Column8" dataDxfId="59"/>
+    <tableColumn id="9" xr3:uid="{C42826CE-029E-4945-8434-CBC9F4DAA57F}" name="Column9" dataDxfId="58" dataCellStyle="Comma"/>
+    <tableColumn id="7" xr3:uid="{F0789B57-A27F-47CD-94AE-4F6B71344DB9}" name="Column92" dataDxfId="57" dataCellStyle="Currency"/>
+    <tableColumn id="13" xr3:uid="{84F8B5AD-93FB-4C3E-8E09-FB358E10FC62}" name="Column93" dataDxfId="56" dataCellStyle="Currency"/>
+    <tableColumn id="14" xr3:uid="{DA8CB162-5C11-45A4-93E0-E0C45C3ED3D0}" name="Column94" dataDxfId="55" dataCellStyle="Comma"/>
+    <tableColumn id="27" xr3:uid="{100A9F62-6915-49BB-B014-4D0BC03BB553}" name="Column95" dataDxfId="54" dataCellStyle="Comma"/>
+    <tableColumn id="10" xr3:uid="{5B60D48A-2B91-4E81-AD9D-2709C1335F32}" name="Column10" dataDxfId="53" dataCellStyle="Comma"/>
+    <tableColumn id="11" xr3:uid="{E1B16D3B-DEA4-44A7-8DE4-CA3F41D77B2B}" name="Column11" dataDxfId="52" dataCellStyle="Comma"/>
+    <tableColumn id="12" xr3:uid="{793817C6-38BE-49BA-A9A6-4F96D87310D9}" name="Column12" dataDxfId="51" dataCellStyle="Comma"/>
+    <tableColumn id="15" xr3:uid="{2AFA675A-D2B0-476D-A865-BB72634DC6DA}" name="Column15" dataDxfId="50"/>
+    <tableColumn id="16" xr3:uid="{B5249436-7148-4EBF-B8E6-5226AA101320}" name="Column16" dataDxfId="49" dataCellStyle="Currency"/>
+    <tableColumn id="17" xr3:uid="{22140E2C-B2EC-4771-8D39-0E8FE9F80B88}" name="Column17" dataDxfId="48"/>
+    <tableColumn id="18" xr3:uid="{AC423A03-E794-4524-9C7D-D02B01892118}" name="Column18" dataDxfId="47" dataCellStyle="Comma"/>
+    <tableColumn id="19" xr3:uid="{F73A917A-F13B-4BB9-8524-E34E6050878C}" name="Column19" dataDxfId="46" dataCellStyle="Comma"/>
+    <tableColumn id="20" xr3:uid="{4A9B484B-EBD7-41D1-8470-161DB87D7FB2}" name="Column20" dataDxfId="45" dataCellStyle="Comma"/>
+    <tableColumn id="21" xr3:uid="{D03D1805-69BB-4D67-B61E-961F2E625E81}" name="Column21" dataDxfId="44"/>
+    <tableColumn id="22" xr3:uid="{66E8E4D1-FF14-404F-8354-025C93AED5CB}" name="Column22" dataDxfId="43"/>
+    <tableColumn id="23" xr3:uid="{9540F131-1C8F-4F4F-8796-92F1AFD57E03}" name="Column23" dataDxfId="42"/>
+    <tableColumn id="24" xr3:uid="{B7156378-CEA1-4808-9801-4E93C755FE92}" name="Column24" dataDxfId="41"/>
+    <tableColumn id="25" xr3:uid="{6908C233-AA1B-4818-BF8F-36FC13C53D09}" name="Column25" dataDxfId="40"/>
+    <tableColumn id="26" xr3:uid="{104781D6-1EEE-4947-A424-3CE3DCADF4CF}" name="Column26" dataDxfId="39"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4109,44 +4109,44 @@
   <tableColumns count="27">
     <tableColumn id="8" xr3:uid="{8CAFE9A2-351C-491C-8F0E-A191FB5F62F1}" name="group"/>
     <tableColumn id="7" xr3:uid="{05D8AE13-6024-4F28-BE04-4F5644C5B73A}" name="sector"/>
-    <tableColumn id="1" xr3:uid="{AFA57C80-2B2F-4727-B322-33373A15C9AE}" name="symbol" dataDxfId="90"/>
-    <tableColumn id="18" xr3:uid="{26F4ADAE-9F47-4523-899C-9F45673EC02E}" name="etf family" dataDxfId="89" dataCellStyle="Comma"/>
-    <tableColumn id="2" xr3:uid="{8D355E55-9FB0-4524-AED7-63AB9F6D6462}" name="etf fee" dataDxfId="88" dataCellStyle="Percent"/>
-    <tableColumn id="10" xr3:uid="{E4D4C04D-8552-411E-A523-CA974B50C63C}" name="90-day avg daily volume" dataDxfId="87" dataCellStyle="Comma"/>
-    <tableColumn id="3" xr3:uid="{FCA124B1-94D2-4B56-BB90-0F7311223FEE}" name="div 2026--09" dataDxfId="86" dataCellStyle="Currency"/>
-    <tableColumn id="16" xr3:uid="{BFBF1D57-673D-4449-B2FA-6EED3331C484}" name="div 2026-09 ex-date" dataDxfId="85" dataCellStyle="Percent"/>
-    <tableColumn id="13" xr3:uid="{F669470C-F245-4562-8E25-5953F248B91F}" name="div 2026-08" dataDxfId="84" dataCellStyle="Currency"/>
-    <tableColumn id="23" xr3:uid="{9D2DF049-DA5F-4A77-8D33-ABB58A4438DC}" name="div 2026-08 ex-date" dataDxfId="83" dataCellStyle="Percent"/>
-    <tableColumn id="11" xr3:uid="{BBCBF25D-DDD4-4D61-8E1E-077BE62554AC}" name="div 2026-07" dataDxfId="82" dataCellStyle="Currency"/>
-    <tableColumn id="22" xr3:uid="{9B510A38-BDAA-4C83-A0BA-CBA8258D1B5A}" name="div 2026-07 ex-date" dataDxfId="81" dataCellStyle="Percent"/>
-    <tableColumn id="14" xr3:uid="{D76D35EB-1AB6-4DE5-8C1C-3111406F2F72}" name="div 2026-06" dataDxfId="80" dataCellStyle="Currency"/>
-    <tableColumn id="6" xr3:uid="{2101D0BE-AB56-44C4-AFF7-91BBB1013C9C}" name="div 2026-06 ex-date" dataDxfId="79" dataCellStyle="Percent"/>
-    <tableColumn id="21" xr3:uid="{82A49A8D-4D68-4D59-B5F9-F90A5262424F}" name="div 2026-05" dataDxfId="78" dataCellStyle="Currency"/>
-    <tableColumn id="24" xr3:uid="{2182D668-9AC5-4102-8F80-1187AFD225B7}" name="div 2026-05 ex-date" dataDxfId="77" dataCellStyle="Percent"/>
-    <tableColumn id="20" xr3:uid="{852173F6-72F7-4C68-BCA3-F7246A86D135}" name="div 2026-04" dataDxfId="76" dataCellStyle="Currency"/>
-    <tableColumn id="25" xr3:uid="{B8A617CB-C02A-4BAC-8397-105FB69C924D}" name="div 2026-04 ex-date" dataDxfId="75" dataCellStyle="Percent"/>
-    <tableColumn id="12" xr3:uid="{9BD4CA41-7A1D-40D5-86AC-FF1C5FE693FF}" name="div 2026-03" dataDxfId="74" dataCellStyle="Currency"/>
-    <tableColumn id="15" xr3:uid="{EE81E628-1DED-4A9A-B38F-77C889074F27}" name="div 2026-03 ex-date" dataDxfId="73" dataCellStyle="Percent"/>
-    <tableColumn id="19" xr3:uid="{3AD8B9FD-8C84-4949-A894-23543B2F48F6}" name="div 2026-02" dataDxfId="72" dataCellStyle="Currency"/>
-    <tableColumn id="26" xr3:uid="{B1AEFFE4-8EA5-4C45-A401-AE133D518FD2}" name="div 2026-02 ex-date" dataDxfId="71" dataCellStyle="Percent"/>
-    <tableColumn id="17" xr3:uid="{A1681DB9-E7FD-4AAD-BF01-80B2684F4CDF}" name="div 2026-01" dataDxfId="70" dataCellStyle="Currency"/>
-    <tableColumn id="27" xr3:uid="{576627EC-6EAC-4067-956A-DF67926726DC}" name="div 2026-01 ex-date" dataDxfId="69" dataCellStyle="Percent"/>
-    <tableColumn id="5" xr3:uid="{6C9795AF-4493-4D80-8BB1-FF32A4E90439}" name=" div 2025-12" dataDxfId="68" dataCellStyle="Currency"/>
-    <tableColumn id="4" xr3:uid="{D716E943-B958-4884-BE63-A9B80B433F62}" name="div 2025-12 ex-date" dataDxfId="67" dataCellStyle="Percent"/>
-    <tableColumn id="9" xr3:uid="{9FCCF7D4-0FBF-4FEE-86E1-9320D1C3E195}" name="comment" dataDxfId="66" dataCellStyle="Currency"/>
+    <tableColumn id="1" xr3:uid="{AFA57C80-2B2F-4727-B322-33373A15C9AE}" name="symbol" dataDxfId="38"/>
+    <tableColumn id="18" xr3:uid="{26F4ADAE-9F47-4523-899C-9F45673EC02E}" name="etf family" dataDxfId="37" dataCellStyle="Comma"/>
+    <tableColumn id="2" xr3:uid="{8D355E55-9FB0-4524-AED7-63AB9F6D6462}" name="etf fee" dataDxfId="36" dataCellStyle="Percent"/>
+    <tableColumn id="10" xr3:uid="{E4D4C04D-8552-411E-A523-CA974B50C63C}" name="90-day avg daily volume" dataDxfId="35" dataCellStyle="Comma"/>
+    <tableColumn id="3" xr3:uid="{FCA124B1-94D2-4B56-BB90-0F7311223FEE}" name="div 2026--09" dataDxfId="34" dataCellStyle="Currency"/>
+    <tableColumn id="16" xr3:uid="{BFBF1D57-673D-4449-B2FA-6EED3331C484}" name="div 2026-09 ex-date" dataDxfId="33" dataCellStyle="Percent"/>
+    <tableColumn id="13" xr3:uid="{F669470C-F245-4562-8E25-5953F248B91F}" name="div 2026-08" dataDxfId="32" dataCellStyle="Currency"/>
+    <tableColumn id="23" xr3:uid="{9D2DF049-DA5F-4A77-8D33-ABB58A4438DC}" name="div 2026-08 ex-date" dataDxfId="31" dataCellStyle="Percent"/>
+    <tableColumn id="11" xr3:uid="{BBCBF25D-DDD4-4D61-8E1E-077BE62554AC}" name="div 2026-07" dataDxfId="30" dataCellStyle="Currency"/>
+    <tableColumn id="22" xr3:uid="{9B510A38-BDAA-4C83-A0BA-CBA8258D1B5A}" name="div 2026-07 ex-date" dataDxfId="29" dataCellStyle="Percent"/>
+    <tableColumn id="14" xr3:uid="{D76D35EB-1AB6-4DE5-8C1C-3111406F2F72}" name="div 2026-06" dataDxfId="28" dataCellStyle="Currency"/>
+    <tableColumn id="6" xr3:uid="{2101D0BE-AB56-44C4-AFF7-91BBB1013C9C}" name="div 2026-06 ex-date" dataDxfId="27" dataCellStyle="Percent"/>
+    <tableColumn id="21" xr3:uid="{82A49A8D-4D68-4D59-B5F9-F90A5262424F}" name="div 2026-05" dataDxfId="26" dataCellStyle="Currency"/>
+    <tableColumn id="24" xr3:uid="{2182D668-9AC5-4102-8F80-1187AFD225B7}" name="div 2026-05 ex-date" dataDxfId="25" dataCellStyle="Percent"/>
+    <tableColumn id="20" xr3:uid="{852173F6-72F7-4C68-BCA3-F7246A86D135}" name="div 2026-04" dataDxfId="24" dataCellStyle="Currency"/>
+    <tableColumn id="25" xr3:uid="{B8A617CB-C02A-4BAC-8397-105FB69C924D}" name="div 2026-04 ex-date" dataDxfId="23" dataCellStyle="Percent"/>
+    <tableColumn id="12" xr3:uid="{9BD4CA41-7A1D-40D5-86AC-FF1C5FE693FF}" name="div 2026-03" dataDxfId="22" dataCellStyle="Currency"/>
+    <tableColumn id="15" xr3:uid="{EE81E628-1DED-4A9A-B38F-77C889074F27}" name="div 2026-03 ex-date" dataDxfId="21" dataCellStyle="Percent"/>
+    <tableColumn id="19" xr3:uid="{3AD8B9FD-8C84-4949-A894-23543B2F48F6}" name="div 2026-02" dataDxfId="20" dataCellStyle="Currency"/>
+    <tableColumn id="26" xr3:uid="{B1AEFFE4-8EA5-4C45-A401-AE133D518FD2}" name="div 2026-02 ex-date" dataDxfId="19" dataCellStyle="Percent"/>
+    <tableColumn id="17" xr3:uid="{A1681DB9-E7FD-4AAD-BF01-80B2684F4CDF}" name="div 2026-01" dataDxfId="18" dataCellStyle="Currency"/>
+    <tableColumn id="27" xr3:uid="{576627EC-6EAC-4067-956A-DF67926726DC}" name="div 2026-01 ex-date" dataDxfId="17" dataCellStyle="Percent"/>
+    <tableColumn id="5" xr3:uid="{6C9795AF-4493-4D80-8BB1-FF32A4E90439}" name=" div 2025-12" dataDxfId="16" dataCellStyle="Currency"/>
+    <tableColumn id="4" xr3:uid="{D716E943-B958-4884-BE63-A9B80B433F62}" name="div 2025-12 ex-date" dataDxfId="15" dataCellStyle="Percent"/>
+    <tableColumn id="9" xr3:uid="{9FCCF7D4-0FBF-4FEE-86E1-9320D1C3E195}" name="comment" dataDxfId="14" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D7EA60E1-CEC4-43C9-8716-3B5D84C5EEA2}" name="mkt_data_streaming_inputs" displayName="mkt_data_streaming_inputs" ref="A1:D13" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D7EA60E1-CEC4-43C9-8716-3B5D84C5EEA2}" name="mkt_data_streaming_inputs" displayName="mkt_data_streaming_inputs" ref="A1:D13" totalsRowShown="0" headerRowDxfId="90" dataDxfId="89">
   <autoFilter ref="A1:D13" xr:uid="{D7EA60E1-CEC4-43C9-8716-3B5D84C5EEA2}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{1B4EEA70-C71C-4CEF-9887-9E40B33F8AAC}" name="Keys" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{5215E933-000B-4891-AE18-89796F5A216B}" name="Crypto" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{A4E0A8E0-4334-4FB9-95BD-3E9FE4AB471E}" name="Stat_Arb_Group" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{16DC4587-9A67-4643-BE5B-698CEC2360C4}" name="BTC_ETF" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{1B4EEA70-C71C-4CEF-9887-9E40B33F8AAC}" name="Keys" dataDxfId="88"/>
+    <tableColumn id="2" xr3:uid="{5215E933-000B-4891-AE18-89796F5A216B}" name="Crypto" dataDxfId="87"/>
+    <tableColumn id="4" xr3:uid="{A4E0A8E0-4334-4FB9-95BD-3E9FE4AB471E}" name="Stat_Arb_Group" dataDxfId="86"/>
+    <tableColumn id="5" xr3:uid="{16DC4587-9A67-4643-BE5B-698CEC2360C4}" name="BTC_ETF" dataDxfId="85"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -26003,7 +26003,7 @@
       </c>
       <c r="D5" s="160" t="str">
         <f ca="1">_xlfn.CONCAT("ETF_",D15,".csv")</f>
-        <v>ETF_2026-09-02.csv</v>
+        <v>ETF_2026-09-03.csv</v>
       </c>
       <c r="E5" s="146"/>
     </row>
@@ -26132,7 +26132,7 @@
     <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D15" s="164" t="str">
         <f t="shared" ref="D15" ca="1" si="0">TEXT(TODAY(),"yyyy-mm-dd")</f>
-        <v>2026-09-02</v>
+        <v>2026-09-03</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" x14ac:dyDescent="0.2">

--- a/spreadsheets/2026 Fin Inst Database.xlsx
+++ b/spreadsheets/2026 Fin Inst Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micha\git-projects\trading\spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762CF3FD-F35C-4BD3-8F9F-6811EA709E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A03B54-9495-4962-8A00-393C4483C47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30510" yWindow="2610" windowWidth="20265" windowHeight="9765" tabRatio="763" firstSheet="3" activeTab="3" xr2:uid="{80E421DC-2A5F-48BD-91BD-DB367A6ED94D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="763" firstSheet="3" activeTab="3" xr2:uid="{80E421DC-2A5F-48BD-91BD-DB367A6ED94D}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="31" r:id="rId1"/>
@@ -4096,15 +4096,9 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4BF31094-215C-402D-8B13-3705F7FDAA90}" name="scalar_inputs_table" displayName="scalar_inputs_table" ref="A1:AA73" totalsRowShown="0">
-  <autoFilter ref="A1:AA73" xr:uid="{09E497BC-17A6-470C-8E05-7E807D85C061}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="fixed income"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AA73" xr:uid="{09E497BC-17A6-470C-8E05-7E807D85C061}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA41">
-    <sortCondition ref="D1:D73"/>
+    <sortCondition ref="A1:A73"/>
   </sortState>
   <tableColumns count="27">
     <tableColumn id="8" xr3:uid="{8CAFE9A2-351C-491C-8F0E-A191FB5F62F1}" name="group"/>
@@ -15093,64 +15087,64 @@
         <v>421</v>
       </c>
       <c r="B2" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>279</v>
+        <v>258</v>
       </c>
       <c r="D2" s="152" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="E2" s="154">
-        <v>2.3E-3</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="F2" s="152">
-        <v>651000</v>
+        <v>9160000</v>
       </c>
       <c r="G2" s="223">
-        <v>0.1</v>
+        <v>0.33710000000000001</v>
       </c>
       <c r="H2" s="211">
         <v>46266</v>
       </c>
       <c r="I2" s="188">
-        <v>0.1</v>
+        <v>0.33756999999999998</v>
       </c>
       <c r="J2" s="211">
         <v>46237</v>
       </c>
       <c r="K2" s="188">
-        <v>0.1</v>
+        <v>0.33068999999999998</v>
       </c>
       <c r="L2" s="211">
         <v>46204</v>
       </c>
       <c r="M2" s="188">
-        <v>0.1</v>
+        <v>0.33149000000000001</v>
       </c>
       <c r="N2" s="211">
         <v>46174</v>
       </c>
       <c r="O2" s="188">
-        <v>0.1</v>
+        <v>0.32993400000000001</v>
       </c>
       <c r="P2" s="211">
         <v>46143</v>
       </c>
       <c r="Q2" s="188">
-        <v>0.1</v>
+        <v>0.33671899999999999</v>
       </c>
       <c r="R2" s="211">
         <v>46113</v>
       </c>
       <c r="S2" s="188">
-        <v>0.1</v>
+        <v>0.31637700000000002</v>
       </c>
       <c r="T2" s="211">
         <v>46083</v>
       </c>
       <c r="U2" s="188">
-        <v>0.1</v>
+        <v>0.32465500000000003</v>
       </c>
       <c r="V2" s="211">
         <v>46055</v>
@@ -15162,10 +15156,10 @@
         <v>87</v>
       </c>
       <c r="Y2" s="188">
-        <v>0.1</v>
+        <v>0.33401199999999998</v>
       </c>
       <c r="Z2" s="211">
-        <v>46021</v>
+        <v>46010</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15176,61 +15170,61 @@
         <v>422</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="D3" s="152" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="E3" s="154">
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="F3" s="152">
-        <v>9160000</v>
+        <v>2140000</v>
       </c>
       <c r="G3" s="223">
-        <v>0.33710000000000001</v>
+        <v>7.6600000000000001E-2</v>
       </c>
       <c r="H3" s="211">
         <v>46266</v>
       </c>
       <c r="I3" s="188">
-        <v>0.33756999999999998</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="J3" s="211">
         <v>46237</v>
       </c>
       <c r="K3" s="188">
-        <v>0.33068999999999998</v>
+        <v>0.08</v>
       </c>
       <c r="L3" s="211">
         <v>46204</v>
       </c>
       <c r="M3" s="188">
-        <v>0.33149000000000001</v>
+        <v>8.09E-2</v>
       </c>
       <c r="N3" s="211">
         <v>46174</v>
       </c>
       <c r="O3" s="188">
-        <v>0.32993400000000001</v>
+        <v>7.8700000000000006E-2</v>
       </c>
       <c r="P3" s="211">
         <v>46143</v>
       </c>
       <c r="Q3" s="188">
-        <v>0.33671899999999999</v>
+        <v>7.85E-2</v>
       </c>
       <c r="R3" s="211">
         <v>46113</v>
       </c>
       <c r="S3" s="188">
-        <v>0.31637700000000002</v>
+        <v>7.7200000000000005E-2</v>
       </c>
       <c r="T3" s="211">
         <v>46083</v>
       </c>
       <c r="U3" s="188">
-        <v>0.32465500000000003</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="V3" s="211">
         <v>46055</v>
@@ -15242,7 +15236,7 @@
         <v>87</v>
       </c>
       <c r="Y3" s="188">
-        <v>0.33401199999999998</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="Z3" s="211">
         <v>46010</v>
@@ -15253,64 +15247,64 @@
         <v>421</v>
       </c>
       <c r="B4" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="D4" s="152" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E4" s="154">
-        <v>8.0000000000000004E-4</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="F4" s="152">
-        <v>481000</v>
+        <v>3320000</v>
       </c>
       <c r="G4" s="223">
-        <v>0.143787</v>
+        <v>8.9305999999999996E-2</v>
       </c>
       <c r="H4" s="211">
         <v>46266</v>
       </c>
       <c r="I4" s="188">
-        <v>0.14026</v>
+        <v>8.8980000000000004E-2</v>
       </c>
       <c r="J4" s="211">
         <v>46237</v>
       </c>
       <c r="K4" s="188">
-        <v>0.14266000000000001</v>
+        <v>8.7480000000000002E-2</v>
       </c>
       <c r="L4" s="211">
         <v>46204</v>
       </c>
       <c r="M4" s="188">
-        <v>0.13805000000000001</v>
+        <v>8.7929999999999994E-2</v>
       </c>
       <c r="N4" s="211">
         <v>46174</v>
       </c>
       <c r="O4" s="188">
-        <v>0.140709</v>
+        <v>8.6389999999999995E-2</v>
       </c>
       <c r="P4" s="211">
         <v>46143</v>
       </c>
       <c r="Q4" s="188">
-        <v>0.14038100000000001</v>
+        <v>8.7540000000000007E-2</v>
       </c>
       <c r="R4" s="211">
         <v>46113</v>
       </c>
       <c r="S4" s="188">
-        <v>0.14212</v>
+        <v>8.3150000000000002E-2</v>
       </c>
       <c r="T4" s="211">
         <v>46083</v>
       </c>
       <c r="U4" s="188">
-        <v>0.13797699999999999</v>
+        <v>8.1979999999999997E-2</v>
       </c>
       <c r="V4" s="211">
         <v>46055</v>
@@ -15322,10 +15316,10 @@
         <v>87</v>
       </c>
       <c r="Y4" s="188">
-        <v>0.139651</v>
+        <v>9.1097999999999998E-2</v>
       </c>
       <c r="Z4" s="211">
-        <v>46010</v>
+        <v>46009</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15333,64 +15327,64 @@
         <v>421</v>
       </c>
       <c r="B5" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>218</v>
+        <v>259</v>
       </c>
       <c r="D5" s="152" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="E5" s="154">
-        <v>2E-3</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="F5" s="152">
-        <v>777000</v>
+        <v>8690000</v>
       </c>
       <c r="G5" s="223">
-        <v>0.134461</v>
+        <v>0.252886</v>
       </c>
       <c r="H5" s="211">
         <v>46266</v>
       </c>
       <c r="I5" s="188">
-        <v>0.13896</v>
+        <v>0.25155</v>
       </c>
       <c r="J5" s="211">
         <v>46237</v>
       </c>
       <c r="K5" s="188">
-        <v>0.12010999999999999</v>
+        <v>0.24446999999999999</v>
       </c>
       <c r="L5" s="211">
         <v>46204</v>
       </c>
       <c r="M5" s="188">
-        <v>0.12951599999999999</v>
+        <v>0.24726000000000001</v>
       </c>
       <c r="N5" s="211">
         <v>46174</v>
       </c>
       <c r="O5" s="188">
-        <v>0.12153</v>
+        <v>0.24171300000000001</v>
       </c>
       <c r="P5" s="211">
         <v>46143</v>
       </c>
       <c r="Q5" s="188">
-        <v>0.133766</v>
+        <v>0.25001600000000002</v>
       </c>
       <c r="R5" s="211">
         <v>46113</v>
       </c>
       <c r="S5" s="188">
-        <v>0.129662</v>
+        <v>0.227824</v>
       </c>
       <c r="T5" s="211">
         <v>46083</v>
       </c>
       <c r="U5" s="188">
-        <v>0.107402</v>
+        <v>0.24546999999999999</v>
       </c>
       <c r="V5" s="211">
         <v>46055</v>
@@ -15402,10 +15396,10 @@
         <v>87</v>
       </c>
       <c r="Y5" s="188">
-        <v>0.21784200000000001</v>
+        <v>0.246638</v>
       </c>
       <c r="Z5" s="211">
-        <v>46010</v>
+        <v>46009</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15413,64 +15407,64 @@
         <v>421</v>
       </c>
       <c r="B6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="D6" s="152" t="s">
         <v>300</v>
       </c>
       <c r="E6" s="154">
-        <v>4.0000000000000002E-4</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="F6" s="152">
-        <v>2460000</v>
+        <v>481000</v>
       </c>
       <c r="G6" s="223">
-        <v>0.20414599999999999</v>
+        <v>0.143787</v>
       </c>
       <c r="H6" s="211">
         <v>46266</v>
       </c>
       <c r="I6" s="188">
-        <v>0.20637</v>
+        <v>0.14026</v>
       </c>
       <c r="J6" s="211">
         <v>46237</v>
       </c>
       <c r="K6" s="188">
-        <v>0.20164000000000001</v>
+        <v>0.14266000000000001</v>
       </c>
       <c r="L6" s="211">
         <v>46204</v>
       </c>
       <c r="M6" s="188">
-        <v>0.20741999999999999</v>
+        <v>0.13805000000000001</v>
       </c>
       <c r="N6" s="211">
         <v>46174</v>
       </c>
       <c r="O6" s="188">
-        <v>0.20424999999999999</v>
+        <v>0.140709</v>
       </c>
       <c r="P6" s="211">
         <v>46143</v>
       </c>
       <c r="Q6" s="188">
-        <v>0.19914000000000001</v>
+        <v>0.14038100000000001</v>
       </c>
       <c r="R6" s="211">
         <v>46113</v>
       </c>
       <c r="S6" s="188">
-        <v>0.20302999999999999</v>
+        <v>0.14212</v>
       </c>
       <c r="T6" s="211">
         <v>46083</v>
       </c>
       <c r="U6" s="188">
-        <v>0.19395999999999999</v>
+        <v>0.13797699999999999</v>
       </c>
       <c r="V6" s="211">
         <v>46055</v>
@@ -15482,7 +15476,7 @@
         <v>87</v>
       </c>
       <c r="Y6" s="188">
-        <v>0.20618</v>
+        <v>0.139651</v>
       </c>
       <c r="Z6" s="211">
         <v>46010</v>
@@ -15493,64 +15487,64 @@
         <v>421</v>
       </c>
       <c r="B7" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="D7" s="152" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="E7" s="154">
-        <v>3.8999999999999998E-3</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="F7" s="152">
-        <v>8170000</v>
+        <v>286000</v>
       </c>
       <c r="G7" s="223">
-        <v>0.41367700000000002</v>
+        <v>0.26019999999999999</v>
       </c>
       <c r="H7" s="211">
         <v>46266</v>
       </c>
       <c r="I7" s="188">
-        <v>0.41359000000000001</v>
+        <v>0.25640000000000002</v>
       </c>
       <c r="J7" s="211">
         <v>46237</v>
       </c>
       <c r="K7" s="188">
-        <v>0.3997</v>
+        <v>0.26240000000000002</v>
       </c>
       <c r="L7" s="211">
         <v>46204</v>
       </c>
       <c r="M7" s="188">
-        <v>0.40704000000000001</v>
+        <v>0.25750000000000001</v>
       </c>
       <c r="N7" s="211">
         <v>46174</v>
       </c>
       <c r="O7" s="188">
-        <v>0.41008</v>
+        <v>0.26029999999999998</v>
       </c>
       <c r="P7" s="211">
         <v>46143</v>
       </c>
       <c r="Q7" s="188">
-        <v>0.45540000000000003</v>
+        <v>0.25819999999999999</v>
       </c>
       <c r="R7" s="211">
         <v>46113</v>
       </c>
       <c r="S7" s="188">
-        <v>0.40295999999999998</v>
+        <v>0.25669999999999998</v>
       </c>
       <c r="T7" s="211">
         <v>46083</v>
       </c>
       <c r="U7" s="188">
-        <v>0.41458</v>
+        <v>0.25080000000000002</v>
       </c>
       <c r="V7" s="211">
         <v>46055</v>
@@ -15562,10 +15556,10 @@
         <v>87</v>
       </c>
       <c r="Y7" s="188">
-        <v>0.38289299999999998</v>
+        <v>0.2626</v>
       </c>
       <c r="Z7" s="211">
-        <v>46010</v>
+        <v>46015</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15573,64 +15567,64 @@
         <v>421</v>
       </c>
       <c r="B8" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D8" s="152" t="s">
         <v>300</v>
       </c>
       <c r="E8" s="154">
-        <v>2.5000000000000001E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="F8" s="152">
-        <v>1120000</v>
+        <v>777000</v>
       </c>
       <c r="G8" s="223">
-        <v>0.14246</v>
+        <v>0.134461</v>
       </c>
       <c r="H8" s="211">
         <v>46266</v>
       </c>
       <c r="I8" s="188">
-        <v>0.14807000000000001</v>
+        <v>0.13896</v>
       </c>
       <c r="J8" s="211">
         <v>46237</v>
       </c>
       <c r="K8" s="188">
-        <v>0.14105000000000001</v>
+        <v>0.12010999999999999</v>
       </c>
       <c r="L8" s="211">
         <v>46204</v>
       </c>
       <c r="M8" s="188">
-        <v>0.14907000000000001</v>
+        <v>0.12951599999999999</v>
       </c>
       <c r="N8" s="211">
         <v>46174</v>
       </c>
       <c r="O8" s="188">
-        <v>0.15162999999999999</v>
+        <v>0.12153</v>
       </c>
       <c r="P8" s="211">
         <v>46143</v>
       </c>
       <c r="Q8" s="188">
-        <v>0.14197000000000001</v>
+        <v>0.133766</v>
       </c>
       <c r="R8" s="211">
         <v>46113</v>
       </c>
       <c r="S8" s="188">
-        <v>0.15057999999999999</v>
+        <v>0.129662</v>
       </c>
       <c r="T8" s="211">
         <v>46083</v>
       </c>
       <c r="U8" s="188">
-        <v>0.14729999999999999</v>
+        <v>0.107402</v>
       </c>
       <c r="V8" s="211">
         <v>46055</v>
@@ -15642,7 +15636,7 @@
         <v>87</v>
       </c>
       <c r="Y8" s="188">
-        <v>0.14660500000000001</v>
+        <v>0.21784200000000001</v>
       </c>
       <c r="Z8" s="211">
         <v>46010</v>
@@ -15653,64 +15647,64 @@
         <v>421</v>
       </c>
       <c r="B9" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>260</v>
+        <v>216</v>
       </c>
       <c r="D9" s="152" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E9" s="154">
-        <v>4.8999999999999998E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="F9" s="152">
-        <v>41300000</v>
+        <v>968000</v>
       </c>
       <c r="G9" s="223">
-        <v>0.435025</v>
+        <v>0.154807</v>
       </c>
       <c r="H9" s="211">
         <v>46266</v>
       </c>
       <c r="I9" s="188">
-        <v>0.38429000000000002</v>
+        <v>0.21054</v>
       </c>
       <c r="J9" s="211">
         <v>46237</v>
       </c>
       <c r="K9" s="188">
-        <v>0.36879000000000001</v>
+        <v>9.1050000000000006E-2</v>
       </c>
       <c r="L9" s="211">
         <v>46204</v>
       </c>
       <c r="M9" s="188">
-        <v>0.40897</v>
+        <v>0.15523000000000001</v>
       </c>
       <c r="N9" s="211">
         <v>46174</v>
       </c>
       <c r="O9" s="188">
-        <v>0.41871000000000003</v>
+        <v>0.12466000000000001</v>
       </c>
       <c r="P9" s="211">
         <v>46143</v>
       </c>
       <c r="Q9" s="188">
-        <v>0.38373000000000002</v>
+        <v>0.10198</v>
       </c>
       <c r="R9" s="211">
         <v>46113</v>
       </c>
       <c r="S9" s="188">
-        <v>0.39373999999999998</v>
+        <v>0.14646999999999999</v>
       </c>
       <c r="T9" s="211">
         <v>46083</v>
       </c>
       <c r="U9" s="188">
-        <v>0.39868999999999999</v>
+        <v>8.6249999999999993E-2</v>
       </c>
       <c r="V9" s="211">
         <v>46055</v>
@@ -15722,10 +15716,10 @@
         <v>87</v>
       </c>
       <c r="Y9" s="188">
-        <v>0.38062400000000002</v>
+        <v>0.16361100000000001</v>
       </c>
       <c r="Z9" s="211">
-        <v>46010</v>
+        <v>46009</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15733,64 +15727,64 @@
         <v>421</v>
       </c>
       <c r="B10" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="D10" s="152" t="s">
         <v>300</v>
       </c>
       <c r="E10" s="154">
-        <v>8.0000000000000004E-4</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="F10" s="152">
-        <v>13550000</v>
+        <v>2460000</v>
       </c>
       <c r="G10" s="223">
-        <v>0.21326600000000001</v>
+        <v>0.20414599999999999</v>
       </c>
       <c r="H10" s="211">
         <v>46266</v>
       </c>
       <c r="I10" s="188">
-        <v>0.21290000000000001</v>
+        <v>0.20637</v>
       </c>
       <c r="J10" s="211">
         <v>46237</v>
       </c>
       <c r="K10" s="188">
-        <v>0.20629</v>
+        <v>0.20164000000000001</v>
       </c>
       <c r="L10" s="211">
         <v>46204</v>
       </c>
       <c r="M10" s="188">
-        <v>0.20932000000000001</v>
+        <v>0.20741999999999999</v>
       </c>
       <c r="N10" s="211">
         <v>46174</v>
       </c>
       <c r="O10" s="188">
-        <v>0.20244999999999999</v>
+        <v>0.20424999999999999</v>
       </c>
       <c r="P10" s="211">
         <v>46143</v>
       </c>
       <c r="Q10" s="188">
-        <v>0.23028999999999999</v>
+        <v>0.19914000000000001</v>
       </c>
       <c r="R10" s="211">
         <v>46113</v>
       </c>
       <c r="S10" s="188">
-        <v>0.20236000000000001</v>
+        <v>0.20302999999999999</v>
       </c>
       <c r="T10" s="211">
         <v>46083</v>
       </c>
       <c r="U10" s="188">
-        <v>0.21539</v>
+        <v>0.19395999999999999</v>
       </c>
       <c r="V10" s="211">
         <v>46055</v>
@@ -15802,7 +15796,7 @@
         <v>87</v>
       </c>
       <c r="Y10" s="188">
-        <v>0.21210300000000001</v>
+        <v>0.20618</v>
       </c>
       <c r="Z10" s="211">
         <v>46010</v>
@@ -15813,64 +15807,64 @@
         <v>421</v>
       </c>
       <c r="B11" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>276</v>
+        <v>255</v>
       </c>
       <c r="D11" s="152" t="s">
-        <v>300</v>
-      </c>
-      <c r="E11" s="154">
-        <v>6.9999999999999999E-4</v>
+        <v>288</v>
+      </c>
+      <c r="E11" s="187">
+        <v>2E-3</v>
       </c>
       <c r="F11" s="152">
-        <v>1540000</v>
+        <v>107000</v>
       </c>
       <c r="G11" s="223">
-        <v>0</v>
-      </c>
-      <c r="H11" s="212">
+        <v>0.39</v>
+      </c>
+      <c r="H11" s="211">
         <v>46266</v>
       </c>
       <c r="I11" s="188">
-        <v>0</v>
-      </c>
-      <c r="J11" s="212" t="s">
-        <v>87</v>
+        <v>0.43</v>
+      </c>
+      <c r="J11" s="211">
+        <v>46237</v>
       </c>
       <c r="K11" s="188">
-        <v>0.41535</v>
+        <v>0.41</v>
       </c>
       <c r="L11" s="211">
         <v>46204</v>
       </c>
       <c r="M11" s="188">
-        <v>0</v>
-      </c>
-      <c r="N11" s="212" t="s">
-        <v>87</v>
+        <v>0.41</v>
+      </c>
+      <c r="N11" s="211">
+        <v>46174</v>
       </c>
       <c r="O11" s="188">
-        <v>0</v>
-      </c>
-      <c r="P11" s="212" t="s">
-        <v>87</v>
+        <v>0.4</v>
+      </c>
+      <c r="P11" s="211">
+        <v>46143</v>
       </c>
       <c r="Q11" s="188">
-        <v>0.19075</v>
+        <v>0.37</v>
       </c>
       <c r="R11" s="211">
         <v>46113</v>
       </c>
       <c r="S11" s="188">
-        <v>0</v>
-      </c>
-      <c r="T11" s="212" t="s">
-        <v>87</v>
+        <v>0.38</v>
+      </c>
+      <c r="T11" s="211">
+        <v>46083</v>
       </c>
       <c r="U11" s="188">
-        <v>0.10698000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="V11" s="211">
         <v>46055</v>
@@ -15882,10 +15876,10 @@
         <v>87</v>
       </c>
       <c r="Y11" s="188">
-        <v>1.5387740000000001</v>
+        <v>0.42</v>
       </c>
       <c r="Z11" s="211">
-        <v>46010</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15893,67 +15887,67 @@
         <v>421</v>
       </c>
       <c r="B12" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="D12" s="152" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E12" s="154">
-        <v>3.5000000000000001E-3</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="F12" s="152">
-        <v>384000</v>
+        <v>628000</v>
       </c>
       <c r="G12" s="223">
-        <v>0</v>
-      </c>
-      <c r="H12" s="212">
+        <v>0.123783</v>
+      </c>
+      <c r="H12" s="211">
         <v>46266</v>
       </c>
       <c r="I12" s="188">
-        <v>0</v>
-      </c>
-      <c r="J12" s="212" t="s">
-        <v>87</v>
+        <v>0.12334000000000001</v>
+      </c>
+      <c r="J12" s="211">
+        <v>46237</v>
       </c>
       <c r="K12" s="188">
-        <v>0</v>
-      </c>
-      <c r="L12" s="212" t="s">
-        <v>87</v>
+        <v>0.12291000000000001</v>
+      </c>
+      <c r="L12" s="211">
+        <v>46204</v>
       </c>
       <c r="M12" s="188">
-        <v>0</v>
-      </c>
-      <c r="N12" s="212" t="s">
-        <v>87</v>
+        <v>0.12291000000000001</v>
+      </c>
+      <c r="N12" s="211">
+        <v>46174</v>
       </c>
       <c r="O12" s="188">
-        <v>0</v>
-      </c>
-      <c r="P12" s="212" t="s">
-        <v>87</v>
+        <v>0.12257</v>
+      </c>
+      <c r="P12" s="211">
+        <v>46143</v>
       </c>
       <c r="Q12" s="188">
-        <v>0</v>
-      </c>
-      <c r="R12" s="212" t="s">
-        <v>87</v>
+        <v>0.12262000000000001</v>
+      </c>
+      <c r="R12" s="211">
+        <v>46113</v>
       </c>
       <c r="S12" s="188">
-        <v>0</v>
-      </c>
-      <c r="T12" s="212" t="s">
-        <v>87</v>
+        <v>0.12246</v>
+      </c>
+      <c r="T12" s="211">
+        <v>46083</v>
       </c>
       <c r="U12" s="188">
-        <v>0</v>
-      </c>
-      <c r="V12" s="212" t="s">
-        <v>87</v>
+        <v>0.12303</v>
+      </c>
+      <c r="V12" s="211">
+        <v>46055</v>
       </c>
       <c r="W12" s="188">
         <v>0</v>
@@ -15962,10 +15956,10 @@
         <v>87</v>
       </c>
       <c r="Y12" s="188">
-        <v>0.58702200000000004</v>
+        <v>0.122505</v>
       </c>
       <c r="Z12" s="211">
-        <v>46010</v>
+        <v>46009</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15973,64 +15967,64 @@
         <v>421</v>
       </c>
       <c r="B13" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>219</v>
+        <v>270</v>
       </c>
       <c r="D13" s="152" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="E13" s="154">
-        <v>4.0000000000000002E-4</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="F13" s="152">
-        <v>1850000</v>
+        <v>104000</v>
       </c>
       <c r="G13" s="223">
-        <v>0.21920000000000001</v>
+        <v>0.32729999999999998</v>
       </c>
       <c r="H13" s="211">
         <v>46266</v>
       </c>
       <c r="I13" s="188">
-        <v>0.20477999999999999</v>
+        <v>0.32619999999999999</v>
       </c>
       <c r="J13" s="211">
         <v>46237</v>
       </c>
       <c r="K13" s="188">
-        <v>0.21489</v>
+        <v>0.316</v>
       </c>
       <c r="L13" s="211">
         <v>46204</v>
       </c>
       <c r="M13" s="188">
-        <v>0.22156000000000001</v>
+        <v>0.31900000000000001</v>
       </c>
       <c r="N13" s="211">
         <v>46174</v>
       </c>
       <c r="O13" s="188">
-        <v>0.21720999999999999</v>
+        <v>0.31409999999999999</v>
       </c>
       <c r="P13" s="211">
         <v>46143</v>
       </c>
       <c r="Q13" s="188">
-        <v>0.23022000000000001</v>
+        <v>0.32269999999999999</v>
       </c>
       <c r="R13" s="211">
         <v>46113</v>
       </c>
       <c r="S13" s="188">
-        <v>0.22142999999999999</v>
+        <v>0.2913</v>
       </c>
       <c r="T13" s="211">
         <v>46083</v>
       </c>
       <c r="U13" s="188">
-        <v>0.22189999999999999</v>
+        <v>0.32369999999999999</v>
       </c>
       <c r="V13" s="211">
         <v>46055</v>
@@ -16042,10 +16036,10 @@
         <v>87</v>
       </c>
       <c r="Y13" s="188">
-        <v>0.21740999999999999</v>
+        <v>0.3105</v>
       </c>
       <c r="Z13" s="211">
-        <v>46010</v>
+        <v>46009</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16053,64 +16047,64 @@
         <v>421</v>
       </c>
       <c r="B14" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>220</v>
+        <v>274</v>
       </c>
       <c r="D14" s="152" t="s">
         <v>300</v>
       </c>
       <c r="E14" s="154">
-        <v>4.0000000000000002E-4</v>
+        <v>3.8999999999999998E-3</v>
       </c>
       <c r="F14" s="152">
-        <v>2490000</v>
+        <v>8170000</v>
       </c>
       <c r="G14" s="223">
-        <v>0.338841</v>
+        <v>0.41367700000000002</v>
       </c>
       <c r="H14" s="211">
         <v>46266</v>
       </c>
       <c r="I14" s="188">
-        <v>0.34133999999999998</v>
+        <v>0.41359000000000001</v>
       </c>
       <c r="J14" s="211">
         <v>46237</v>
       </c>
       <c r="K14" s="188">
-        <v>0.33732000000000001</v>
+        <v>0.3997</v>
       </c>
       <c r="L14" s="211">
         <v>46204</v>
       </c>
       <c r="M14" s="188">
-        <v>0.33339999999999997</v>
+        <v>0.40704000000000001</v>
       </c>
       <c r="N14" s="211">
         <v>46174</v>
       </c>
       <c r="O14" s="188">
-        <v>0.33465</v>
+        <v>0.41008</v>
       </c>
       <c r="P14" s="211">
         <v>46143</v>
       </c>
       <c r="Q14" s="188">
-        <v>0.33295000000000002</v>
+        <v>0.45540000000000003</v>
       </c>
       <c r="R14" s="211">
         <v>46113</v>
       </c>
       <c r="S14" s="188">
-        <v>0.32777000000000001</v>
+        <v>0.40295999999999998</v>
       </c>
       <c r="T14" s="211">
         <v>46083</v>
       </c>
       <c r="U14" s="188">
-        <v>0.33472000000000002</v>
+        <v>0.41458</v>
       </c>
       <c r="V14" s="211">
         <v>46055</v>
@@ -16122,7 +16116,7 @@
         <v>87</v>
       </c>
       <c r="Y14" s="188">
-        <v>0.33404800000000001</v>
+        <v>0.38289299999999998</v>
       </c>
       <c r="Z14" s="211">
         <v>46010</v>
@@ -16133,64 +16127,64 @@
         <v>421</v>
       </c>
       <c r="B15" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>221</v>
+        <v>282</v>
       </c>
       <c r="D15" s="152" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="E15" s="154">
-        <v>5.0000000000000001E-4</v>
+        <v>1.5E-3</v>
       </c>
       <c r="F15" s="152">
-        <v>3800000</v>
+        <v>650000</v>
       </c>
       <c r="G15" s="223">
-        <v>0.28987299999999999</v>
+        <v>0.32069999999999999</v>
       </c>
       <c r="H15" s="211">
         <v>46266</v>
       </c>
       <c r="I15" s="188">
-        <v>0.2863</v>
+        <v>0.34660000000000002</v>
       </c>
       <c r="J15" s="211">
         <v>46237</v>
       </c>
       <c r="K15" s="188">
-        <v>0.28858</v>
+        <v>0.31369999999999998</v>
       </c>
       <c r="L15" s="211">
         <v>46204</v>
       </c>
       <c r="M15" s="188">
-        <v>0.27983999999999998</v>
+        <v>0.31890000000000002</v>
       </c>
       <c r="N15" s="211">
         <v>46174</v>
       </c>
       <c r="O15" s="188">
-        <v>0.28893000000000002</v>
+        <v>0.318</v>
       </c>
       <c r="P15" s="211">
         <v>46143</v>
       </c>
       <c r="Q15" s="188">
-        <v>0.28211999999999998</v>
+        <v>0.32879999999999998</v>
       </c>
       <c r="R15" s="211">
         <v>46113</v>
       </c>
       <c r="S15" s="188">
-        <v>0.29221999999999998</v>
+        <v>0.3196</v>
       </c>
       <c r="T15" s="211">
         <v>46083</v>
       </c>
       <c r="U15" s="188">
-        <v>0.27905000000000002</v>
+        <v>0.33960000000000001</v>
       </c>
       <c r="V15" s="211">
         <v>46055</v>
@@ -16202,10 +16196,10 @@
         <v>87</v>
       </c>
       <c r="Y15" s="188">
-        <v>0.285497</v>
+        <v>0.31519999999999998</v>
       </c>
       <c r="Z15" s="211">
-        <v>46010</v>
+        <v>46009</v>
       </c>
     </row>
     <row r="16" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16213,64 +16207,64 @@
         <v>421</v>
       </c>
       <c r="B16" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>278</v>
+        <v>217</v>
       </c>
       <c r="D16" s="152" t="s">
         <v>300</v>
       </c>
       <c r="E16" s="154">
-        <v>4.4999999999999997E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="F16" s="152">
-        <v>3230000</v>
+        <v>1120000</v>
       </c>
       <c r="G16" s="223">
-        <v>0.14724200000000001</v>
+        <v>0.14246</v>
       </c>
       <c r="H16" s="211">
         <v>46266</v>
       </c>
       <c r="I16" s="188">
-        <v>0.14230999999999999</v>
+        <v>0.14807000000000001</v>
       </c>
       <c r="J16" s="211">
         <v>46237</v>
       </c>
       <c r="K16" s="188">
-        <v>0.14174</v>
+        <v>0.14105000000000001</v>
       </c>
       <c r="L16" s="211">
         <v>46204</v>
       </c>
       <c r="M16" s="188">
-        <v>0.13839699999999999</v>
+        <v>0.14907000000000001</v>
       </c>
       <c r="N16" s="211">
         <v>46174</v>
       </c>
       <c r="O16" s="188">
-        <v>0.14032500000000001</v>
+        <v>0.15162999999999999</v>
       </c>
       <c r="P16" s="211">
         <v>46143</v>
       </c>
       <c r="Q16" s="188">
-        <v>0.14196700000000001</v>
+        <v>0.14197000000000001</v>
       </c>
       <c r="R16" s="211">
         <v>46113</v>
       </c>
       <c r="S16" s="188">
-        <v>3.1167E-2</v>
+        <v>0.15057999999999999</v>
       </c>
       <c r="T16" s="211">
         <v>46083</v>
       </c>
       <c r="U16" s="188">
-        <v>0.17722599999999999</v>
+        <v>0.14729999999999999</v>
       </c>
       <c r="V16" s="211">
         <v>46055</v>
@@ -16282,7 +16276,7 @@
         <v>87</v>
       </c>
       <c r="Y16" s="188">
-        <v>6.5883999999999998E-2</v>
+        <v>0.14660500000000001</v>
       </c>
       <c r="Z16" s="211">
         <v>46010</v>
@@ -16293,64 +16287,64 @@
         <v>421</v>
       </c>
       <c r="B17" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>255</v>
+        <v>215</v>
       </c>
       <c r="D17" s="152" t="s">
-        <v>288</v>
-      </c>
-      <c r="E17" s="187">
-        <v>2E-3</v>
+        <v>286</v>
+      </c>
+      <c r="E17" s="154">
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="F17" s="152">
-        <v>107000</v>
+        <v>872000</v>
       </c>
       <c r="G17" s="223">
-        <v>0.39</v>
+        <v>0.159</v>
       </c>
       <c r="H17" s="211">
         <v>46266</v>
       </c>
       <c r="I17" s="188">
-        <v>0.43</v>
+        <v>0.16839999999999999</v>
       </c>
       <c r="J17" s="211">
         <v>46237</v>
       </c>
       <c r="K17" s="188">
-        <v>0.41</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="L17" s="211">
         <v>46204</v>
       </c>
       <c r="M17" s="188">
-        <v>0.41</v>
+        <v>0.1535</v>
       </c>
       <c r="N17" s="211">
         <v>46174</v>
       </c>
       <c r="O17" s="188">
-        <v>0.4</v>
+        <v>0.15629999999999999</v>
       </c>
       <c r="P17" s="211">
         <v>46143</v>
       </c>
       <c r="Q17" s="188">
-        <v>0.37</v>
+        <v>0.17449999999999999</v>
       </c>
       <c r="R17" s="211">
         <v>46113</v>
       </c>
       <c r="S17" s="188">
-        <v>0.38</v>
+        <v>0.14050000000000001</v>
       </c>
       <c r="T17" s="211">
         <v>46083</v>
       </c>
       <c r="U17" s="188">
-        <v>0.37</v>
+        <v>0.15909999999999999</v>
       </c>
       <c r="V17" s="211">
         <v>46055</v>
@@ -16362,10 +16356,10 @@
         <v>87</v>
       </c>
       <c r="Y17" s="188">
-        <v>0.42</v>
+        <v>0.15989999999999999</v>
       </c>
       <c r="Z17" s="211">
-        <v>46022</v>
+        <v>46020</v>
       </c>
     </row>
     <row r="18" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16373,64 +16367,64 @@
         <v>421</v>
       </c>
       <c r="B18" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D18" s="152" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="E18" s="154">
-        <v>2.9999999999999997E-4</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="F18" s="152">
-        <v>2140000</v>
+        <v>41300000</v>
       </c>
       <c r="G18" s="223">
-        <v>7.6600000000000001E-2</v>
+        <v>0.435025</v>
       </c>
       <c r="H18" s="211">
         <v>46266</v>
       </c>
       <c r="I18" s="188">
-        <v>8.7999999999999995E-2</v>
+        <v>0.38429000000000002</v>
       </c>
       <c r="J18" s="211">
         <v>46237</v>
       </c>
       <c r="K18" s="188">
-        <v>0.08</v>
+        <v>0.36879000000000001</v>
       </c>
       <c r="L18" s="211">
         <v>46204</v>
       </c>
       <c r="M18" s="188">
-        <v>8.09E-2</v>
+        <v>0.40897</v>
       </c>
       <c r="N18" s="211">
         <v>46174</v>
       </c>
       <c r="O18" s="188">
-        <v>7.8700000000000006E-2</v>
+        <v>0.41871000000000003</v>
       </c>
       <c r="P18" s="211">
         <v>46143</v>
       </c>
       <c r="Q18" s="188">
-        <v>7.85E-2</v>
+        <v>0.38373000000000002</v>
       </c>
       <c r="R18" s="211">
         <v>46113</v>
       </c>
       <c r="S18" s="188">
-        <v>7.7200000000000005E-2</v>
+        <v>0.39373999999999998</v>
       </c>
       <c r="T18" s="211">
         <v>46083</v>
       </c>
       <c r="U18" s="188">
-        <v>8.5000000000000006E-2</v>
+        <v>0.39868999999999999</v>
       </c>
       <c r="V18" s="211">
         <v>46055</v>
@@ -16442,7 +16436,7 @@
         <v>87</v>
       </c>
       <c r="Y18" s="188">
-        <v>7.6999999999999999E-2</v>
+        <v>0.38062400000000002</v>
       </c>
       <c r="Z18" s="211">
         <v>46010</v>
@@ -16456,61 +16450,61 @@
         <v>431</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D19" s="152" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="E19" s="154">
-        <v>2.9999999999999997E-4</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="F19" s="152">
-        <v>1180000</v>
+        <v>13550000</v>
       </c>
       <c r="G19" s="223">
-        <v>0.1396</v>
+        <v>0.21326600000000001</v>
       </c>
       <c r="H19" s="211">
         <v>46266</v>
       </c>
       <c r="I19" s="188">
-        <v>0.1547</v>
+        <v>0.21290000000000001</v>
       </c>
       <c r="J19" s="211">
         <v>46237</v>
       </c>
       <c r="K19" s="188">
-        <v>0.1487</v>
+        <v>0.20629</v>
       </c>
       <c r="L19" s="211">
         <v>46204</v>
       </c>
       <c r="M19" s="188">
-        <v>0.14960000000000001</v>
+        <v>0.20932000000000001</v>
       </c>
       <c r="N19" s="211">
         <v>46174</v>
       </c>
       <c r="O19" s="188">
-        <v>0.1449</v>
+        <v>0.20244999999999999</v>
       </c>
       <c r="P19" s="211">
         <v>46143</v>
       </c>
       <c r="Q19" s="188">
-        <v>0.1537</v>
+        <v>0.23028999999999999</v>
       </c>
       <c r="R19" s="211">
         <v>46113</v>
       </c>
       <c r="S19" s="188">
-        <v>0.1449</v>
+        <v>0.20236000000000001</v>
       </c>
       <c r="T19" s="211">
         <v>46083</v>
       </c>
       <c r="U19" s="188">
-        <v>0.15579999999999999</v>
+        <v>0.21539</v>
       </c>
       <c r="V19" s="211">
         <v>46055</v>
@@ -16522,7 +16516,7 @@
         <v>87</v>
       </c>
       <c r="Y19" s="188">
-        <v>0.14810000000000001</v>
+        <v>0.21210300000000001</v>
       </c>
       <c r="Z19" s="211">
         <v>46010</v>
@@ -16533,10 +16527,10 @@
         <v>421</v>
       </c>
       <c r="B20" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>222</v>
+        <v>265</v>
       </c>
       <c r="D20" s="152" t="s">
         <v>291</v>
@@ -16545,22 +16539,22 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="F20" s="152">
-        <v>760000</v>
+        <v>1180000</v>
       </c>
       <c r="G20" s="223">
-        <v>0.10929999999999999</v>
+        <v>0.1396</v>
       </c>
       <c r="H20" s="211">
         <v>46266</v>
       </c>
       <c r="I20" s="188">
-        <v>0.127</v>
+        <v>0.1547</v>
       </c>
       <c r="J20" s="211">
         <v>46237</v>
       </c>
       <c r="K20" s="188">
-        <v>0.1085</v>
+        <v>0.1487</v>
       </c>
       <c r="L20" s="211">
         <v>46204</v>
@@ -16572,25 +16566,25 @@
         <v>46174</v>
       </c>
       <c r="O20" s="188">
-        <v>0.1168</v>
+        <v>0.1449</v>
       </c>
       <c r="P20" s="211">
         <v>46143</v>
       </c>
       <c r="Q20" s="188">
-        <v>0.12770000000000001</v>
+        <v>0.1537</v>
       </c>
       <c r="R20" s="211">
         <v>46113</v>
       </c>
       <c r="S20" s="188">
-        <v>0.1066</v>
+        <v>0.1449</v>
       </c>
       <c r="T20" s="211">
         <v>46083</v>
       </c>
       <c r="U20" s="188">
-        <v>0.14799999999999999</v>
+        <v>0.15579999999999999</v>
       </c>
       <c r="V20" s="211">
         <v>46055</v>
@@ -16602,7 +16596,7 @@
         <v>87</v>
       </c>
       <c r="Y20" s="188">
-        <v>0.127</v>
+        <v>0.14810000000000001</v>
       </c>
       <c r="Z20" s="211">
         <v>46010</v>
@@ -16613,64 +16607,64 @@
         <v>421</v>
       </c>
       <c r="B21" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D21" s="152" t="s">
         <v>301</v>
       </c>
       <c r="E21" s="154">
-        <v>2.9999999999999997E-4</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="F21" s="152">
-        <v>3320000</v>
+        <v>2800000</v>
       </c>
       <c r="G21" s="223">
-        <v>8.9305999999999996E-2</v>
+        <v>0.53229499999999996</v>
       </c>
       <c r="H21" s="211">
         <v>46266</v>
       </c>
       <c r="I21" s="188">
-        <v>8.8980000000000004E-2</v>
+        <v>0.52717999999999998</v>
       </c>
       <c r="J21" s="211">
         <v>46237</v>
       </c>
       <c r="K21" s="188">
-        <v>8.7480000000000002E-2</v>
+        <v>0.53078000000000003</v>
       </c>
       <c r="L21" s="211">
         <v>46204</v>
       </c>
       <c r="M21" s="188">
-        <v>8.7929999999999994E-2</v>
+        <v>0.52310000000000001</v>
       </c>
       <c r="N21" s="211">
         <v>46174</v>
       </c>
       <c r="O21" s="188">
-        <v>8.6389999999999995E-2</v>
+        <v>0.52693999999999996</v>
       </c>
       <c r="P21" s="211">
         <v>46143</v>
       </c>
       <c r="Q21" s="188">
-        <v>8.7540000000000007E-2</v>
+        <v>0.52478000000000002</v>
       </c>
       <c r="R21" s="211">
         <v>46113</v>
       </c>
       <c r="S21" s="188">
-        <v>8.3150000000000002E-2</v>
+        <v>0.52456999999999998</v>
       </c>
       <c r="T21" s="211">
         <v>46083</v>
       </c>
       <c r="U21" s="188">
-        <v>8.1979999999999997E-2</v>
+        <v>0.56008999999999998</v>
       </c>
       <c r="V21" s="211">
         <v>46055</v>
@@ -16682,7 +16676,7 @@
         <v>87</v>
       </c>
       <c r="Y21" s="188">
-        <v>9.1097999999999998E-2</v>
+        <v>0.49054799999999998</v>
       </c>
       <c r="Z21" s="211">
         <v>46009</v>
@@ -16694,64 +16688,64 @@
         <v>421</v>
       </c>
       <c r="B22" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>216</v>
+        <v>267</v>
       </c>
       <c r="D22" s="152" t="s">
         <v>301</v>
       </c>
       <c r="E22" s="154">
-        <v>4.0000000000000001E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="F22" s="152">
-        <v>968000</v>
+        <v>5830000</v>
       </c>
       <c r="G22" s="223">
-        <v>0.154807</v>
+        <v>0.14036100000000001</v>
       </c>
       <c r="H22" s="211">
         <v>46266</v>
       </c>
       <c r="I22" s="188">
-        <v>0.21054</v>
+        <v>0.13564999999999999</v>
       </c>
       <c r="J22" s="211">
         <v>46237</v>
       </c>
       <c r="K22" s="188">
-        <v>9.1050000000000006E-2</v>
+        <v>0.13818</v>
       </c>
       <c r="L22" s="211">
         <v>46204</v>
       </c>
       <c r="M22" s="188">
-        <v>0.15523000000000001</v>
+        <v>0.13750999999999999</v>
       </c>
       <c r="N22" s="211">
         <v>46174</v>
       </c>
       <c r="O22" s="188">
-        <v>0.12466000000000001</v>
+        <v>0.13657</v>
       </c>
       <c r="P22" s="211">
         <v>46143</v>
       </c>
       <c r="Q22" s="188">
-        <v>0.10198</v>
+        <v>0.13836000000000001</v>
       </c>
       <c r="R22" s="211">
         <v>46113</v>
       </c>
       <c r="S22" s="188">
-        <v>0.14646999999999999</v>
+        <v>0.13963999999999999</v>
       </c>
       <c r="T22" s="211">
         <v>46083</v>
       </c>
       <c r="U22" s="188">
-        <v>8.6249999999999993E-2</v>
+        <v>0.13791</v>
       </c>
       <c r="V22" s="211">
         <v>46055</v>
@@ -16763,7 +16757,7 @@
         <v>87</v>
       </c>
       <c r="Y22" s="188">
-        <v>0.16361100000000001</v>
+        <v>0.140677</v>
       </c>
       <c r="Z22" s="211">
         <v>46009</v>
@@ -16774,64 +16768,64 @@
         <v>421</v>
       </c>
       <c r="B23" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D23" s="152" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="E23" s="154">
-        <v>2.9999999999999997E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="F23" s="152">
-        <v>628000</v>
+        <v>1530000</v>
       </c>
       <c r="G23" s="223">
-        <v>0.123783</v>
+        <v>0.19292999999999999</v>
       </c>
       <c r="H23" s="211">
         <v>46266</v>
       </c>
       <c r="I23" s="188">
-        <v>0.12334000000000001</v>
+        <v>0.20161999999999999</v>
       </c>
       <c r="J23" s="211">
         <v>46237</v>
       </c>
       <c r="K23" s="188">
-        <v>0.12291000000000001</v>
+        <v>0.19264999999999999</v>
       </c>
       <c r="L23" s="211">
         <v>46204</v>
       </c>
       <c r="M23" s="188">
-        <v>0.12291000000000001</v>
+        <v>0.19889999999999999</v>
       </c>
       <c r="N23" s="211">
         <v>46174</v>
       </c>
       <c r="O23" s="188">
-        <v>0.12257</v>
+        <v>0.18801999999999999</v>
       </c>
       <c r="P23" s="211">
         <v>46143</v>
       </c>
       <c r="Q23" s="188">
-        <v>0.12262000000000001</v>
+        <v>0.22111</v>
       </c>
       <c r="R23" s="211">
         <v>46113</v>
       </c>
       <c r="S23" s="188">
-        <v>0.12246</v>
+        <v>0.17266000000000001</v>
       </c>
       <c r="T23" s="211">
         <v>46083</v>
       </c>
       <c r="U23" s="188">
-        <v>0.12303</v>
+        <v>0.20602999999999999</v>
       </c>
       <c r="V23" s="211">
         <v>46055</v>
@@ -16843,10 +16837,10 @@
         <v>87</v>
       </c>
       <c r="Y23" s="188">
-        <v>0.122505</v>
+        <v>0.20891000000000001</v>
       </c>
       <c r="Z23" s="211">
-        <v>46009</v>
+        <v>46013</v>
       </c>
     </row>
     <row r="24" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16854,64 +16848,64 @@
         <v>421</v>
       </c>
       <c r="B24" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="D24" s="152" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E24" s="154">
-        <v>4.0000000000000001E-3</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="F24" s="152">
-        <v>2800000</v>
+        <v>1540000</v>
       </c>
       <c r="G24" s="223">
-        <v>0.53229499999999996</v>
-      </c>
-      <c r="H24" s="211">
+        <v>0</v>
+      </c>
+      <c r="H24" s="212">
         <v>46266</v>
       </c>
       <c r="I24" s="188">
-        <v>0.52717999999999998</v>
-      </c>
-      <c r="J24" s="211">
-        <v>46237</v>
+        <v>0</v>
+      </c>
+      <c r="J24" s="212" t="s">
+        <v>87</v>
       </c>
       <c r="K24" s="188">
-        <v>0.53078000000000003</v>
+        <v>0.41535</v>
       </c>
       <c r="L24" s="211">
         <v>46204</v>
       </c>
       <c r="M24" s="188">
-        <v>0.52310000000000001</v>
-      </c>
-      <c r="N24" s="211">
-        <v>46174</v>
+        <v>0</v>
+      </c>
+      <c r="N24" s="212" t="s">
+        <v>87</v>
       </c>
       <c r="O24" s="188">
-        <v>0.52693999999999996</v>
-      </c>
-      <c r="P24" s="211">
-        <v>46143</v>
+        <v>0</v>
+      </c>
+      <c r="P24" s="212" t="s">
+        <v>87</v>
       </c>
       <c r="Q24" s="188">
-        <v>0.52478000000000002</v>
+        <v>0.19075</v>
       </c>
       <c r="R24" s="211">
         <v>46113</v>
       </c>
       <c r="S24" s="188">
-        <v>0.52456999999999998</v>
-      </c>
-      <c r="T24" s="211">
-        <v>46083</v>
+        <v>0</v>
+      </c>
+      <c r="T24" s="212" t="s">
+        <v>87</v>
       </c>
       <c r="U24" s="188">
-        <v>0.56008999999999998</v>
+        <v>0.10698000000000001</v>
       </c>
       <c r="V24" s="211">
         <v>46055</v>
@@ -16923,10 +16917,10 @@
         <v>87</v>
       </c>
       <c r="Y24" s="188">
-        <v>0.49054799999999998</v>
+        <v>1.5387740000000001</v>
       </c>
       <c r="Z24" s="211">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="AB24" s="102"/>
     </row>
@@ -16935,64 +16929,64 @@
         <v>421</v>
       </c>
       <c r="B25" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D25" s="152" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="E25" s="154">
-        <v>5.0000000000000001E-4</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="F25" s="152">
-        <v>5830000</v>
+        <v>5160000</v>
       </c>
       <c r="G25" s="223">
-        <v>0.14036100000000001</v>
+        <v>0.1206</v>
       </c>
       <c r="H25" s="211">
         <v>46266</v>
       </c>
       <c r="I25" s="188">
-        <v>0.13564999999999999</v>
+        <v>0.11849999999999999</v>
       </c>
       <c r="J25" s="211">
         <v>46237</v>
       </c>
       <c r="K25" s="188">
-        <v>0.13818</v>
+        <v>0.11119999999999999</v>
       </c>
       <c r="L25" s="211">
         <v>46204</v>
       </c>
       <c r="M25" s="188">
-        <v>0.13750999999999999</v>
+        <v>0.11409999999999999</v>
       </c>
       <c r="N25" s="211">
         <v>46174</v>
       </c>
       <c r="O25" s="188">
-        <v>0.13657</v>
+        <v>0.11260000000000001</v>
       </c>
       <c r="P25" s="211">
         <v>46143</v>
       </c>
       <c r="Q25" s="188">
-        <v>0.13836000000000001</v>
+        <v>0.11169999999999999</v>
       </c>
       <c r="R25" s="211">
         <v>46113</v>
       </c>
       <c r="S25" s="188">
-        <v>0.13963999999999999</v>
+        <v>9.98E-2</v>
       </c>
       <c r="T25" s="211">
         <v>46083</v>
       </c>
       <c r="U25" s="188">
-        <v>0.13791</v>
+        <v>0.1124</v>
       </c>
       <c r="V25" s="211">
         <v>46055</v>
@@ -17004,7 +16998,7 @@
         <v>87</v>
       </c>
       <c r="Y25" s="188">
-        <v>0.140677</v>
+        <v>0.96860000000000002</v>
       </c>
       <c r="Z25" s="211">
         <v>46009</v>
@@ -17018,64 +17012,64 @@
         <v>425</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="D26" s="152" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E26" s="154">
         <v>3.5000000000000001E-3</v>
       </c>
       <c r="F26" s="152">
-        <v>341000</v>
+        <v>384000</v>
       </c>
       <c r="G26" s="223">
-        <v>4.4215999999999998E-2</v>
-      </c>
-      <c r="H26" s="211">
+        <v>0</v>
+      </c>
+      <c r="H26" s="212">
         <v>46266</v>
       </c>
       <c r="I26" s="188">
-        <v>4.546E-2</v>
-      </c>
-      <c r="J26" s="211">
-        <v>46237</v>
+        <v>0</v>
+      </c>
+      <c r="J26" s="212" t="s">
+        <v>87</v>
       </c>
       <c r="K26" s="188">
-        <v>4.4130000000000003E-2</v>
-      </c>
-      <c r="L26" s="211">
-        <v>46204</v>
+        <v>0</v>
+      </c>
+      <c r="L26" s="212" t="s">
+        <v>87</v>
       </c>
       <c r="M26" s="188">
-        <v>4.5019999999999998E-2</v>
-      </c>
-      <c r="N26" s="211">
-        <v>46174</v>
+        <v>0</v>
+      </c>
+      <c r="N26" s="212" t="s">
+        <v>87</v>
       </c>
       <c r="O26" s="188">
-        <v>4.3720000000000002E-2</v>
-      </c>
-      <c r="P26" s="211">
-        <v>46143</v>
+        <v>0</v>
+      </c>
+      <c r="P26" s="212" t="s">
+        <v>87</v>
       </c>
       <c r="Q26" s="188">
-        <v>4.5359999999999998E-2</v>
-      </c>
-      <c r="R26" s="211">
-        <v>46113</v>
+        <v>0</v>
+      </c>
+      <c r="R26" s="212" t="s">
+        <v>87</v>
       </c>
       <c r="S26" s="188">
-        <v>4.0980000000000003E-2</v>
-      </c>
-      <c r="T26" s="211">
-        <v>46083</v>
+        <v>0</v>
+      </c>
+      <c r="T26" s="212" t="s">
+        <v>87</v>
       </c>
       <c r="U26" s="188">
-        <v>3.8260000000000002E-2</v>
-      </c>
-      <c r="V26" s="211">
-        <v>46055</v>
+        <v>0</v>
+      </c>
+      <c r="V26" s="212" t="s">
+        <v>87</v>
       </c>
       <c r="W26" s="188">
         <v>0</v>
@@ -17084,10 +17078,10 @@
         <v>87</v>
       </c>
       <c r="Y26" s="188">
-        <v>0</v>
+        <v>0.58702200000000004</v>
       </c>
       <c r="Z26" s="211">
-        <v>46009</v>
+        <v>46010</v>
       </c>
     </row>
     <row r="27" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17095,64 +17089,64 @@
         <v>421</v>
       </c>
       <c r="B27" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>223</v>
+        <v>272</v>
       </c>
       <c r="D27" s="152" t="s">
         <v>301</v>
       </c>
       <c r="E27" s="154">
-        <v>4.0000000000000002E-4</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="F27" s="152">
-        <v>4040000</v>
+        <v>341000</v>
       </c>
       <c r="G27" s="223">
-        <v>0.10195799999999999</v>
+        <v>4.4215999999999998E-2</v>
       </c>
       <c r="H27" s="211">
         <v>46266</v>
       </c>
       <c r="I27" s="188">
-        <v>0.10152</v>
+        <v>4.546E-2</v>
       </c>
       <c r="J27" s="211">
         <v>46237</v>
       </c>
       <c r="K27" s="188">
-        <v>0.10116</v>
+        <v>4.4130000000000003E-2</v>
       </c>
       <c r="L27" s="211">
         <v>46204</v>
       </c>
       <c r="M27" s="188">
-        <v>0.10147</v>
+        <v>4.5019999999999998E-2</v>
       </c>
       <c r="N27" s="211">
         <v>46174</v>
       </c>
       <c r="O27" s="188">
-        <v>0.10135</v>
+        <v>4.3720000000000002E-2</v>
       </c>
       <c r="P27" s="211">
         <v>46143</v>
       </c>
       <c r="Q27" s="188">
-        <v>0.10022</v>
+        <v>4.5359999999999998E-2</v>
       </c>
       <c r="R27" s="211">
         <v>46113</v>
       </c>
       <c r="S27" s="188">
-        <v>0.10045999999999999</v>
+        <v>4.0980000000000003E-2</v>
       </c>
       <c r="T27" s="211">
         <v>46083</v>
       </c>
       <c r="U27" s="188">
-        <v>0.10298</v>
+        <v>3.8260000000000002E-2</v>
       </c>
       <c r="V27" s="211">
         <v>46055</v>
@@ -17164,7 +17158,7 @@
         <v>87</v>
       </c>
       <c r="Y27" s="188">
-        <v>9.6627000000000005E-2</v>
+        <v>0</v>
       </c>
       <c r="Z27" s="211">
         <v>46009</v>
@@ -17175,64 +17169,64 @@
         <v>421</v>
       </c>
       <c r="B28" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D28" s="152" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E28" s="154">
-        <v>2.9999999999999997E-4</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="F28" s="152">
-        <v>6500000</v>
+        <v>1850000</v>
       </c>
       <c r="G28" s="223">
-        <v>9.3530000000000002E-2</v>
+        <v>0.21920000000000001</v>
       </c>
       <c r="H28" s="211">
         <v>46266</v>
       </c>
       <c r="I28" s="188">
-        <v>9.3149999999999997E-2</v>
+        <v>0.20477999999999999</v>
       </c>
       <c r="J28" s="211">
         <v>46237</v>
       </c>
       <c r="K28" s="188">
-        <v>8.9810000000000001E-2</v>
+        <v>0.21489</v>
       </c>
       <c r="L28" s="211">
         <v>46204</v>
       </c>
       <c r="M28" s="188">
-        <v>9.2770000000000005E-2</v>
+        <v>0.22156000000000001</v>
       </c>
       <c r="N28" s="211">
         <v>46174</v>
       </c>
       <c r="O28" s="188">
-        <v>9.0139999999999998E-2</v>
+        <v>0.21720999999999999</v>
       </c>
       <c r="P28" s="211">
         <v>46143</v>
       </c>
       <c r="Q28" s="188">
-        <v>9.3600000000000003E-2</v>
+        <v>0.23022000000000001</v>
       </c>
       <c r="R28" s="211">
         <v>46113</v>
       </c>
       <c r="S28" s="188">
-        <v>8.3930000000000005E-2</v>
+        <v>0.22142999999999999</v>
       </c>
       <c r="T28" s="211">
         <v>46083</v>
       </c>
       <c r="U28" s="188">
-        <v>9.2689999999999995E-2</v>
+        <v>0.22189999999999999</v>
       </c>
       <c r="V28" s="211">
         <v>46055</v>
@@ -17244,10 +17238,10 @@
         <v>87</v>
       </c>
       <c r="Y28" s="188">
-        <v>9.2302999999999996E-2</v>
+        <v>0.21740999999999999</v>
       </c>
       <c r="Z28" s="211">
-        <v>46009</v>
+        <v>46010</v>
       </c>
     </row>
     <row r="29" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17255,10 +17249,10 @@
         <v>421</v>
       </c>
       <c r="B29" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D29" s="152" t="s">
         <v>301</v>
@@ -17267,52 +17261,52 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="F29" s="152">
-        <v>1030000</v>
+        <v>4040000</v>
       </c>
       <c r="G29" s="223">
-        <v>7.1248000000000006E-2</v>
+        <v>0.10195799999999999</v>
       </c>
       <c r="H29" s="211">
         <v>46266</v>
       </c>
       <c r="I29" s="188">
-        <v>7.1599999999999997E-2</v>
+        <v>0.10152</v>
       </c>
       <c r="J29" s="211">
         <v>46237</v>
       </c>
       <c r="K29" s="188">
-        <v>7.0730000000000001E-2</v>
+        <v>0.10116</v>
       </c>
       <c r="L29" s="211">
         <v>46204</v>
       </c>
       <c r="M29" s="188">
-        <v>7.0120000000000002E-2</v>
+        <v>0.10147</v>
       </c>
       <c r="N29" s="211">
         <v>46174</v>
       </c>
       <c r="O29" s="188">
-        <v>6.9989999999999997E-2</v>
+        <v>0.10135</v>
       </c>
       <c r="P29" s="211">
         <v>46143</v>
       </c>
       <c r="Q29" s="188">
-        <v>7.0129999999999998E-2</v>
+        <v>0.10022</v>
       </c>
       <c r="R29" s="211">
         <v>46113</v>
       </c>
       <c r="S29" s="188">
-        <v>6.9449999999999998E-2</v>
+        <v>0.10045999999999999</v>
       </c>
       <c r="T29" s="211">
         <v>46083</v>
       </c>
       <c r="U29" s="188">
-        <v>7.1540000000000006E-2</v>
+        <v>0.10298</v>
       </c>
       <c r="V29" s="211">
         <v>46055</v>
@@ -17324,7 +17318,7 @@
         <v>87</v>
       </c>
       <c r="Y29" s="188">
-        <v>0.14300099999999999</v>
+        <v>9.6627000000000005E-2</v>
       </c>
       <c r="Z29" s="211">
         <v>46009</v>
@@ -17335,64 +17329,64 @@
         <v>421</v>
       </c>
       <c r="B30" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D30" s="152" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="E30" s="154">
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="F30" s="152">
-        <v>469000</v>
+        <v>5330000</v>
       </c>
       <c r="G30" s="223">
-        <v>0.13560700000000001</v>
+        <v>0.36149999999999999</v>
       </c>
       <c r="H30" s="211">
         <v>46266</v>
       </c>
       <c r="I30" s="188">
-        <v>0.1351</v>
+        <v>0.35020000000000001</v>
       </c>
       <c r="J30" s="211">
         <v>46237</v>
       </c>
       <c r="K30" s="188">
-        <v>0.13542999999999999</v>
+        <v>0.3422</v>
       </c>
       <c r="L30" s="211">
         <v>46204</v>
       </c>
       <c r="M30" s="188">
-        <v>0.13396</v>
+        <v>0.35510000000000003</v>
       </c>
       <c r="N30" s="211">
         <v>46174</v>
       </c>
       <c r="O30" s="188">
-        <v>0.13463</v>
+        <v>0.32740000000000002</v>
       </c>
       <c r="P30" s="211">
         <v>46143</v>
       </c>
       <c r="Q30" s="188">
-        <v>0.13347000000000001</v>
+        <v>0.35610000000000003</v>
       </c>
       <c r="R30" s="211">
         <v>46113</v>
       </c>
       <c r="S30" s="188">
-        <v>0.13635</v>
+        <v>0.31809999999999999</v>
       </c>
       <c r="T30" s="211">
         <v>46083</v>
       </c>
       <c r="U30" s="188">
-        <v>0.13150000000000001</v>
+        <v>0.34560000000000002</v>
       </c>
       <c r="V30" s="211">
         <v>46055</v>
@@ -17404,7 +17398,7 @@
         <v>87</v>
       </c>
       <c r="Y30" s="188">
-        <v>0.13450899999999999</v>
+        <v>0.34920000000000001</v>
       </c>
       <c r="Z30" s="211">
         <v>46009</v>
@@ -17415,64 +17409,64 @@
         <v>421</v>
       </c>
       <c r="B31" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D31" s="152" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E31" s="154">
-        <v>2.5000000000000001E-3</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="F31" s="152">
-        <v>872000</v>
+        <v>760000</v>
       </c>
       <c r="G31" s="223">
-        <v>0.159</v>
+        <v>0.10929999999999999</v>
       </c>
       <c r="H31" s="211">
         <v>46266</v>
       </c>
       <c r="I31" s="188">
-        <v>0.16839999999999999</v>
+        <v>0.127</v>
       </c>
       <c r="J31" s="211">
         <v>46237</v>
       </c>
       <c r="K31" s="188">
-        <v>0.17100000000000001</v>
+        <v>0.1085</v>
       </c>
       <c r="L31" s="211">
         <v>46204</v>
       </c>
       <c r="M31" s="188">
-        <v>0.1535</v>
+        <v>0.14960000000000001</v>
       </c>
       <c r="N31" s="211">
         <v>46174</v>
       </c>
       <c r="O31" s="188">
-        <v>0.15629999999999999</v>
+        <v>0.1168</v>
       </c>
       <c r="P31" s="211">
         <v>46143</v>
       </c>
       <c r="Q31" s="188">
-        <v>0.17449999999999999</v>
+        <v>0.12770000000000001</v>
       </c>
       <c r="R31" s="211">
         <v>46113</v>
       </c>
       <c r="S31" s="188">
-        <v>0.14050000000000001</v>
+        <v>0.1066</v>
       </c>
       <c r="T31" s="211">
         <v>46083</v>
       </c>
       <c r="U31" s="188">
-        <v>0.15909999999999999</v>
+        <v>0.14799999999999999</v>
       </c>
       <c r="V31" s="211">
         <v>46055</v>
@@ -17484,10 +17478,10 @@
         <v>87</v>
       </c>
       <c r="Y31" s="188">
-        <v>0.15989999999999999</v>
+        <v>0.127</v>
       </c>
       <c r="Z31" s="211">
-        <v>46020</v>
+        <v>46010</v>
       </c>
     </row>
     <row r="32" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17495,64 +17489,64 @@
         <v>421</v>
       </c>
       <c r="B32" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>259</v>
+        <v>225</v>
       </c>
       <c r="D32" s="152" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="E32" s="154">
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="F32" s="152">
-        <v>8690000</v>
+        <v>6500000</v>
       </c>
       <c r="G32" s="223">
-        <v>0.252886</v>
+        <v>9.3530000000000002E-2</v>
       </c>
       <c r="H32" s="211">
         <v>46266</v>
       </c>
       <c r="I32" s="188">
-        <v>0.25155</v>
+        <v>9.3149999999999997E-2</v>
       </c>
       <c r="J32" s="211">
         <v>46237</v>
       </c>
       <c r="K32" s="188">
-        <v>0.24446999999999999</v>
+        <v>8.9810000000000001E-2</v>
       </c>
       <c r="L32" s="211">
         <v>46204</v>
       </c>
       <c r="M32" s="188">
-        <v>0.24726000000000001</v>
+        <v>9.2770000000000005E-2</v>
       </c>
       <c r="N32" s="211">
         <v>46174</v>
       </c>
       <c r="O32" s="188">
-        <v>0.24171300000000001</v>
+        <v>9.0139999999999998E-2</v>
       </c>
       <c r="P32" s="211">
         <v>46143</v>
       </c>
       <c r="Q32" s="188">
-        <v>0.25001600000000002</v>
+        <v>9.3600000000000003E-2</v>
       </c>
       <c r="R32" s="211">
         <v>46113</v>
       </c>
       <c r="S32" s="188">
-        <v>0.227824</v>
+        <v>8.3930000000000005E-2</v>
       </c>
       <c r="T32" s="211">
         <v>46083</v>
       </c>
       <c r="U32" s="188">
-        <v>0.24546999999999999</v>
+        <v>9.2689999999999995E-2</v>
       </c>
       <c r="V32" s="211">
         <v>46055</v>
@@ -17564,7 +17558,7 @@
         <v>87</v>
       </c>
       <c r="Y32" s="188">
-        <v>0.246638</v>
+        <v>9.2302999999999996E-2</v>
       </c>
       <c r="Z32" s="211">
         <v>46009</v>
@@ -17575,64 +17569,64 @@
         <v>421</v>
       </c>
       <c r="B33" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>281</v>
+        <v>229</v>
       </c>
       <c r="D33" s="152" t="s">
         <v>287</v>
       </c>
       <c r="E33" s="154">
-        <v>5.9999999999999995E-4</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="F33" s="152">
-        <v>286000</v>
+        <v>3000000</v>
       </c>
       <c r="G33" s="223">
-        <v>0.26019999999999999</v>
+        <v>0.21529999999999999</v>
       </c>
       <c r="H33" s="211">
         <v>46266</v>
       </c>
       <c r="I33" s="188">
-        <v>0.25640000000000002</v>
+        <v>0.2145</v>
       </c>
       <c r="J33" s="211">
         <v>46237</v>
       </c>
       <c r="K33" s="188">
-        <v>0.26240000000000002</v>
+        <v>0.20760000000000001</v>
       </c>
       <c r="L33" s="211">
         <v>46204</v>
       </c>
       <c r="M33" s="188">
-        <v>0.25750000000000001</v>
+        <v>0.21410000000000001</v>
       </c>
       <c r="N33" s="211">
         <v>46174</v>
       </c>
       <c r="O33" s="188">
-        <v>0.26029999999999998</v>
+        <v>0.2099</v>
       </c>
       <c r="P33" s="211">
         <v>46143</v>
       </c>
       <c r="Q33" s="188">
-        <v>0.25819999999999999</v>
+        <v>0.2258</v>
       </c>
       <c r="R33" s="211">
         <v>46113</v>
       </c>
       <c r="S33" s="188">
-        <v>0.25669999999999998</v>
+        <v>0.18740000000000001</v>
       </c>
       <c r="T33" s="211">
         <v>46083</v>
       </c>
       <c r="U33" s="188">
-        <v>0.25080000000000002</v>
+        <v>0.2145</v>
       </c>
       <c r="V33" s="211">
         <v>46055</v>
@@ -17644,10 +17638,10 @@
         <v>87</v>
       </c>
       <c r="Y33" s="188">
-        <v>0.2626</v>
+        <v>0.214</v>
       </c>
       <c r="Z33" s="211">
-        <v>46015</v>
+        <v>46009</v>
       </c>
     </row>
     <row r="34" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17655,64 +17649,64 @@
         <v>421</v>
       </c>
       <c r="B34" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="D34" s="152" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="E34" s="154">
-        <v>2.9999999999999997E-4</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="F34" s="152">
-        <v>104000</v>
+        <v>2490000</v>
       </c>
       <c r="G34" s="223">
-        <v>0.32729999999999998</v>
+        <v>0.338841</v>
       </c>
       <c r="H34" s="211">
         <v>46266</v>
       </c>
       <c r="I34" s="188">
-        <v>0.32619999999999999</v>
+        <v>0.34133999999999998</v>
       </c>
       <c r="J34" s="211">
         <v>46237</v>
       </c>
       <c r="K34" s="188">
-        <v>0.316</v>
+        <v>0.33732000000000001</v>
       </c>
       <c r="L34" s="211">
         <v>46204</v>
       </c>
       <c r="M34" s="188">
-        <v>0.31900000000000001</v>
+        <v>0.33339999999999997</v>
       </c>
       <c r="N34" s="211">
         <v>46174</v>
       </c>
       <c r="O34" s="188">
-        <v>0.31409999999999999</v>
+        <v>0.33465</v>
       </c>
       <c r="P34" s="211">
         <v>46143</v>
       </c>
       <c r="Q34" s="188">
-        <v>0.32269999999999999</v>
+        <v>0.33295000000000002</v>
       </c>
       <c r="R34" s="211">
         <v>46113</v>
       </c>
       <c r="S34" s="188">
-        <v>0.2913</v>
+        <v>0.32777000000000001</v>
       </c>
       <c r="T34" s="211">
         <v>46083</v>
       </c>
       <c r="U34" s="188">
-        <v>0.32369999999999999</v>
+        <v>0.33472000000000002</v>
       </c>
       <c r="V34" s="211">
         <v>46055</v>
@@ -17724,10 +17718,10 @@
         <v>87</v>
       </c>
       <c r="Y34" s="188">
-        <v>0.3105</v>
+        <v>0.33404800000000001</v>
       </c>
       <c r="Z34" s="211">
-        <v>46009</v>
+        <v>46010</v>
       </c>
     </row>
     <row r="35" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17735,64 +17729,64 @@
         <v>421</v>
       </c>
       <c r="B35" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>282</v>
+        <v>224</v>
       </c>
       <c r="D35" s="152" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="E35" s="154">
-        <v>1.5E-3</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="F35" s="152">
-        <v>650000</v>
+        <v>1030000</v>
       </c>
       <c r="G35" s="223">
-        <v>0.32069999999999999</v>
+        <v>7.1248000000000006E-2</v>
       </c>
       <c r="H35" s="211">
         <v>46266</v>
       </c>
       <c r="I35" s="188">
-        <v>0.34660000000000002</v>
+        <v>7.1599999999999997E-2</v>
       </c>
       <c r="J35" s="211">
         <v>46237</v>
       </c>
       <c r="K35" s="188">
-        <v>0.31369999999999998</v>
+        <v>7.0730000000000001E-2</v>
       </c>
       <c r="L35" s="211">
         <v>46204</v>
       </c>
       <c r="M35" s="188">
-        <v>0.31890000000000002</v>
+        <v>7.0120000000000002E-2</v>
       </c>
       <c r="N35" s="211">
         <v>46174</v>
       </c>
       <c r="O35" s="188">
-        <v>0.318</v>
+        <v>6.9989999999999997E-2</v>
       </c>
       <c r="P35" s="211">
         <v>46143</v>
       </c>
       <c r="Q35" s="188">
-        <v>0.32879999999999998</v>
+        <v>7.0129999999999998E-2</v>
       </c>
       <c r="R35" s="211">
         <v>46113</v>
       </c>
       <c r="S35" s="188">
-        <v>0.3196</v>
+        <v>6.9449999999999998E-2</v>
       </c>
       <c r="T35" s="211">
         <v>46083</v>
       </c>
       <c r="U35" s="188">
-        <v>0.33960000000000001</v>
+        <v>7.1540000000000006E-2</v>
       </c>
       <c r="V35" s="211">
         <v>46055</v>
@@ -17804,7 +17798,7 @@
         <v>87</v>
       </c>
       <c r="Y35" s="188">
-        <v>0.31519999999999998</v>
+        <v>0.14300099999999999</v>
       </c>
       <c r="Z35" s="211">
         <v>46009</v>
@@ -17815,64 +17809,64 @@
         <v>421</v>
       </c>
       <c r="B36" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>271</v>
+        <v>230</v>
       </c>
       <c r="D36" s="152" t="s">
         <v>287</v>
       </c>
       <c r="E36" s="154">
-        <v>6.9999999999999999E-4</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="F36" s="152">
-        <v>5160000</v>
+        <v>1570000</v>
       </c>
       <c r="G36" s="223">
-        <v>0.1206</v>
+        <v>0.1666</v>
       </c>
       <c r="H36" s="211">
         <v>46266</v>
       </c>
       <c r="I36" s="188">
-        <v>0.11849999999999999</v>
+        <v>0.16800000000000001</v>
       </c>
       <c r="J36" s="211">
         <v>46237</v>
       </c>
       <c r="K36" s="188">
-        <v>0.11119999999999999</v>
+        <v>0.16450000000000001</v>
       </c>
       <c r="L36" s="211">
         <v>46204</v>
       </c>
       <c r="M36" s="188">
-        <v>0.11409999999999999</v>
+        <v>0.16339999999999999</v>
       </c>
       <c r="N36" s="211">
         <v>46174</v>
       </c>
       <c r="O36" s="188">
-        <v>0.11260000000000001</v>
+        <v>0.16089999999999999</v>
       </c>
       <c r="P36" s="211">
         <v>46143</v>
       </c>
       <c r="Q36" s="188">
-        <v>0.11169999999999999</v>
+        <v>0.16170000000000001</v>
       </c>
       <c r="R36" s="211">
         <v>46113</v>
       </c>
       <c r="S36" s="188">
-        <v>9.98E-2</v>
+        <v>0.16089999999999999</v>
       </c>
       <c r="T36" s="211">
         <v>46083</v>
       </c>
       <c r="U36" s="188">
-        <v>0.1124</v>
+        <v>0.16450000000000001</v>
       </c>
       <c r="V36" s="211">
         <v>46055</v>
@@ -17884,7 +17878,7 @@
         <v>87</v>
       </c>
       <c r="Y36" s="188">
-        <v>0.96860000000000002</v>
+        <v>0.15989999999999999</v>
       </c>
       <c r="Z36" s="211">
         <v>46009</v>
@@ -17895,64 +17889,64 @@
         <v>421</v>
       </c>
       <c r="B37" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="D37" s="152" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="E37" s="154">
-        <v>2.9999999999999997E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="F37" s="152">
-        <v>5330000</v>
+        <v>3800000</v>
       </c>
       <c r="G37" s="223">
-        <v>0.36149999999999999</v>
+        <v>0.28987299999999999</v>
       </c>
       <c r="H37" s="211">
         <v>46266</v>
       </c>
       <c r="I37" s="188">
-        <v>0.35020000000000001</v>
+        <v>0.2863</v>
       </c>
       <c r="J37" s="211">
         <v>46237</v>
       </c>
       <c r="K37" s="188">
-        <v>0.3422</v>
+        <v>0.28858</v>
       </c>
       <c r="L37" s="211">
         <v>46204</v>
       </c>
       <c r="M37" s="188">
-        <v>0.35510000000000003</v>
+        <v>0.27983999999999998</v>
       </c>
       <c r="N37" s="211">
         <v>46174</v>
       </c>
       <c r="O37" s="188">
-        <v>0.32740000000000002</v>
+        <v>0.28893000000000002</v>
       </c>
       <c r="P37" s="211">
         <v>46143</v>
       </c>
       <c r="Q37" s="188">
-        <v>0.35610000000000003</v>
+        <v>0.28211999999999998</v>
       </c>
       <c r="R37" s="211">
         <v>46113</v>
       </c>
       <c r="S37" s="188">
-        <v>0.31809999999999999</v>
+        <v>0.29221999999999998</v>
       </c>
       <c r="T37" s="211">
         <v>46083</v>
       </c>
       <c r="U37" s="188">
-        <v>0.34560000000000002</v>
+        <v>0.27905000000000002</v>
       </c>
       <c r="V37" s="211">
         <v>46055</v>
@@ -17964,10 +17958,10 @@
         <v>87</v>
       </c>
       <c r="Y37" s="188">
-        <v>0.34920000000000001</v>
+        <v>0.285497</v>
       </c>
       <c r="Z37" s="211">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="AA37"/>
     </row>
@@ -17976,64 +17970,64 @@
         <v>421</v>
       </c>
       <c r="B38" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D38" s="152" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="E38" s="154">
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="F38" s="152">
-        <v>3000000</v>
+        <v>469000</v>
       </c>
       <c r="G38" s="223">
-        <v>0.21529999999999999</v>
+        <v>0.13560700000000001</v>
       </c>
       <c r="H38" s="211">
         <v>46266</v>
       </c>
       <c r="I38" s="188">
-        <v>0.2145</v>
+        <v>0.1351</v>
       </c>
       <c r="J38" s="211">
         <v>46237</v>
       </c>
       <c r="K38" s="188">
-        <v>0.20760000000000001</v>
+        <v>0.13542999999999999</v>
       </c>
       <c r="L38" s="211">
         <v>46204</v>
       </c>
       <c r="M38" s="188">
-        <v>0.21410000000000001</v>
+        <v>0.13396</v>
       </c>
       <c r="N38" s="211">
         <v>46174</v>
       </c>
       <c r="O38" s="188">
-        <v>0.2099</v>
+        <v>0.13463</v>
       </c>
       <c r="P38" s="211">
         <v>46143</v>
       </c>
       <c r="Q38" s="188">
-        <v>0.2258</v>
+        <v>0.13347000000000001</v>
       </c>
       <c r="R38" s="211">
         <v>46113</v>
       </c>
       <c r="S38" s="188">
-        <v>0.18740000000000001</v>
+        <v>0.13635</v>
       </c>
       <c r="T38" s="211">
         <v>46083</v>
       </c>
       <c r="U38" s="188">
-        <v>0.2145</v>
+        <v>0.13150000000000001</v>
       </c>
       <c r="V38" s="211">
         <v>46055</v>
@@ -18045,7 +18039,7 @@
         <v>87</v>
       </c>
       <c r="Y38" s="188">
-        <v>0.214</v>
+        <v>0.13450899999999999</v>
       </c>
       <c r="Z38" s="211">
         <v>46009</v>
@@ -18056,10 +18050,10 @@
         <v>421</v>
       </c>
       <c r="B39" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D39" s="152" t="s">
         <v>287</v>
@@ -18068,52 +18062,52 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="F39" s="152">
-        <v>1570000</v>
+        <v>7560000</v>
       </c>
       <c r="G39" s="223">
-        <v>0.1666</v>
+        <v>0.1434</v>
       </c>
       <c r="H39" s="211">
         <v>46266</v>
       </c>
       <c r="I39" s="188">
-        <v>0.16800000000000001</v>
+        <v>0.14149999999999999</v>
       </c>
       <c r="J39" s="211">
         <v>46237</v>
       </c>
       <c r="K39" s="188">
-        <v>0.16450000000000001</v>
+        <v>0.14199999999999999</v>
       </c>
       <c r="L39" s="211">
         <v>46204</v>
       </c>
       <c r="M39" s="188">
-        <v>0.16339999999999999</v>
+        <v>0.1381</v>
       </c>
       <c r="N39" s="211">
         <v>46174</v>
       </c>
       <c r="O39" s="188">
-        <v>0.16089999999999999</v>
+        <v>0.14230000000000001</v>
       </c>
       <c r="P39" s="211">
         <v>46143</v>
       </c>
       <c r="Q39" s="188">
-        <v>0.16170000000000001</v>
+        <v>0.14149999999999999</v>
       </c>
       <c r="R39" s="211">
         <v>46113</v>
       </c>
       <c r="S39" s="188">
-        <v>0.16089999999999999</v>
+        <v>0.1487</v>
       </c>
       <c r="T39" s="211">
         <v>46083</v>
       </c>
       <c r="U39" s="188">
-        <v>0.16450000000000001</v>
+        <v>0.13980000000000001</v>
       </c>
       <c r="V39" s="211">
         <v>46055</v>
@@ -18125,7 +18119,7 @@
         <v>87</v>
       </c>
       <c r="Y39" s="188">
-        <v>0.15989999999999999</v>
+        <v>0.14169999999999999</v>
       </c>
       <c r="Z39" s="211">
         <v>46009</v>
@@ -18136,64 +18130,64 @@
         <v>421</v>
       </c>
       <c r="B40" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>231</v>
+        <v>279</v>
       </c>
       <c r="D40" s="152" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E40" s="154">
-        <v>2.9999999999999997E-4</v>
+        <v>2.3E-3</v>
       </c>
       <c r="F40" s="152">
-        <v>7560000</v>
+        <v>651000</v>
       </c>
       <c r="G40" s="223">
-        <v>0.1434</v>
+        <v>0.1</v>
       </c>
       <c r="H40" s="211">
         <v>46266</v>
       </c>
       <c r="I40" s="188">
-        <v>0.14149999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="J40" s="211">
         <v>46237</v>
       </c>
       <c r="K40" s="188">
-        <v>0.14199999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="L40" s="211">
         <v>46204</v>
       </c>
       <c r="M40" s="188">
-        <v>0.1381</v>
+        <v>0.1</v>
       </c>
       <c r="N40" s="211">
         <v>46174</v>
       </c>
       <c r="O40" s="188">
-        <v>0.14230000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="P40" s="211">
         <v>46143</v>
       </c>
       <c r="Q40" s="188">
-        <v>0.14149999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="R40" s="211">
         <v>46113</v>
       </c>
       <c r="S40" s="188">
-        <v>0.1487</v>
+        <v>0.1</v>
       </c>
       <c r="T40" s="211">
         <v>46083</v>
       </c>
       <c r="U40" s="188">
-        <v>0.13980000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="V40" s="211">
         <v>46055</v>
@@ -18205,10 +18199,10 @@
         <v>87</v>
       </c>
       <c r="Y40" s="188">
-        <v>0.14169999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="Z40" s="211">
-        <v>46009</v>
+        <v>46021</v>
       </c>
     </row>
     <row r="41" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18216,64 +18210,64 @@
         <v>421</v>
       </c>
       <c r="B41" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="D41" s="152" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="E41" s="154">
-        <v>5.0000000000000001E-4</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="F41" s="152">
-        <v>1530000</v>
+        <v>3230000</v>
       </c>
       <c r="G41" s="223">
-        <v>0.19292999999999999</v>
+        <v>0.14724200000000001</v>
       </c>
       <c r="H41" s="211">
         <v>46266</v>
       </c>
       <c r="I41" s="188">
-        <v>0.20161999999999999</v>
+        <v>0.14230999999999999</v>
       </c>
       <c r="J41" s="211">
         <v>46237</v>
       </c>
       <c r="K41" s="188">
-        <v>0.19264999999999999</v>
+        <v>0.14174</v>
       </c>
       <c r="L41" s="211">
         <v>46204</v>
       </c>
       <c r="M41" s="188">
-        <v>0.19889999999999999</v>
+        <v>0.13839699999999999</v>
       </c>
       <c r="N41" s="211">
         <v>46174</v>
       </c>
       <c r="O41" s="188">
-        <v>0.18801999999999999</v>
+        <v>0.14032500000000001</v>
       </c>
       <c r="P41" s="211">
         <v>46143</v>
       </c>
       <c r="Q41" s="188">
-        <v>0.22111</v>
+        <v>0.14196700000000001</v>
       </c>
       <c r="R41" s="211">
         <v>46113</v>
       </c>
       <c r="S41" s="188">
-        <v>0.17266000000000001</v>
+        <v>3.1167E-2</v>
       </c>
       <c r="T41" s="211">
         <v>46083</v>
       </c>
       <c r="U41" s="188">
-        <v>0.20602999999999999</v>
+        <v>0.17722599999999999</v>
       </c>
       <c r="V41" s="211">
         <v>46055</v>
@@ -18285,13 +18279,13 @@
         <v>87</v>
       </c>
       <c r="Y41" s="188">
-        <v>0.20891000000000001</v>
+        <v>6.5883999999999998E-2</v>
       </c>
       <c r="Z41" s="211">
-        <v>46013</v>
-      </c>
-    </row>
-    <row r="42" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>46010</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>401</v>
       </c>
@@ -18370,7 +18364,7 @@
       </c>
       <c r="AA42" s="156"/>
     </row>
-    <row r="43" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>401</v>
       </c>
@@ -18449,7 +18443,7 @@
       </c>
       <c r="AA43" s="156"/>
     </row>
-    <row r="44" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>401</v>
       </c>
@@ -18528,7 +18522,7 @@
       </c>
       <c r="AA44" s="156"/>
     </row>
-    <row r="45" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>401</v>
       </c>
@@ -18607,7 +18601,7 @@
       </c>
       <c r="AA45" s="156"/>
     </row>
-    <row r="46" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>401</v>
       </c>
@@ -18686,7 +18680,7 @@
       </c>
       <c r="AA46" s="156"/>
     </row>
-    <row r="47" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>401</v>
       </c>
@@ -18765,7 +18759,7 @@
       </c>
       <c r="AA47" s="156"/>
     </row>
-    <row r="48" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>401</v>
       </c>
@@ -18844,7 +18838,7 @@
       </c>
       <c r="AA48" s="156"/>
     </row>
-    <row r="49" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>401</v>
       </c>
@@ -18923,7 +18917,7 @@
       </c>
       <c r="AA49" s="156"/>
     </row>
-    <row r="50" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>401</v>
       </c>
@@ -19002,7 +18996,7 @@
       </c>
       <c r="AA50" s="156"/>
     </row>
-    <row r="51" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>401</v>
       </c>
@@ -19081,7 +19075,7 @@
       </c>
       <c r="AA51" s="156"/>
     </row>
-    <row r="52" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>401</v>
       </c>
@@ -19160,7 +19154,7 @@
       </c>
       <c r="AA52" s="156"/>
     </row>
-    <row r="53" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>401</v>
       </c>
@@ -19239,7 +19233,7 @@
       </c>
       <c r="AA53" s="156"/>
     </row>
-    <row r="54" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>401</v>
       </c>
@@ -19318,7 +19312,7 @@
       </c>
       <c r="AA54" s="156"/>
     </row>
-    <row r="55" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>401</v>
       </c>
@@ -19397,7 +19391,7 @@
       </c>
       <c r="AA55" s="156"/>
     </row>
-    <row r="56" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>401</v>
       </c>
@@ -19476,7 +19470,7 @@
       </c>
       <c r="AA56" s="156"/>
     </row>
-    <row r="57" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>401</v>
       </c>
@@ -19555,7 +19549,7 @@
       </c>
       <c r="AA57" s="156"/>
     </row>
-    <row r="58" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>401</v>
       </c>
@@ -19634,7 +19628,7 @@
       </c>
       <c r="AA58" s="156"/>
     </row>
-    <row r="59" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>401</v>
       </c>
@@ -19713,7 +19707,7 @@
       </c>
       <c r="AA59" s="156"/>
     </row>
-    <row r="60" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>401</v>
       </c>
@@ -19792,7 +19786,7 @@
       </c>
       <c r="AA60" s="156"/>
     </row>
-    <row r="61" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>401</v>
       </c>
@@ -19870,7 +19864,7 @@
         <v>46008</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>401</v>
       </c>
@@ -19949,7 +19943,7 @@
       </c>
       <c r="AA62" s="156"/>
     </row>
-    <row r="63" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>401</v>
       </c>
@@ -20028,7 +20022,7 @@
       </c>
       <c r="AA63" s="156"/>
     </row>
-    <row r="64" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>401</v>
       </c>
@@ -20107,7 +20101,7 @@
       </c>
       <c r="AA64" s="156"/>
     </row>
-    <row r="65" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>401</v>
       </c>
@@ -20186,7 +20180,7 @@
       </c>
       <c r="AA65" s="156"/>
     </row>
-    <row r="66" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>401</v>
       </c>
@@ -20265,7 +20259,7 @@
       </c>
       <c r="AA66" s="156"/>
     </row>
-    <row r="67" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>401</v>
       </c>
@@ -20344,7 +20338,7 @@
       </c>
       <c r="AA67" s="156"/>
     </row>
-    <row r="68" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>401</v>
       </c>
@@ -20423,7 +20417,7 @@
       </c>
       <c r="AA68" s="156"/>
     </row>
-    <row r="69" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>401</v>
       </c>
@@ -20502,7 +20496,7 @@
       </c>
       <c r="AA69" s="156"/>
     </row>
-    <row r="70" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>401</v>
       </c>
@@ -20581,7 +20575,7 @@
       </c>
       <c r="AA70" s="156"/>
     </row>
-    <row r="71" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>401</v>
       </c>
@@ -20660,7 +20654,7 @@
       </c>
       <c r="AA71" s="156"/>
     </row>
-    <row r="72" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>401</v>
       </c>
@@ -20739,7 +20733,7 @@
       </c>
       <c r="AA72" s="156"/>
     </row>
-    <row r="73" spans="1:27" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>401</v>
       </c>
@@ -26003,7 +25997,7 @@
       </c>
       <c r="D5" s="160" t="str">
         <f ca="1">_xlfn.CONCAT("ETF_",D15,".csv")</f>
-        <v>ETF_2026-09-03.csv</v>
+        <v>ETF_2026-09-04.csv</v>
       </c>
       <c r="E5" s="146"/>
     </row>
@@ -26132,7 +26126,7 @@
     <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D15" s="164" t="str">
         <f t="shared" ref="D15" ca="1" si="0">TEXT(TODAY(),"yyyy-mm-dd")</f>
-        <v>2026-09-03</v>
+        <v>2026-09-04</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" x14ac:dyDescent="0.2">
